--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -67,7 +67,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFc00000"/>
+      <color rgb="FFed7d31"/>
       <sz val="10"/>
     </font>
     <font>
@@ -79,7 +79,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFed7d31"/>
+      <color rgb="FFc00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -674,9 +674,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -686,10 +683,13 @@
     <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -701,7 +701,7 @@
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1249,9 +1249,21 @@
 11 cables for RMAC/RDOS not arrived yet  1P X 1.0 OS FR 275m</t>
         </is>
       </c>
-      <c r="H3" s="63" t="inlineStr"/>
-      <c r="I3" s="63" t="inlineStr"/>
-      <c r="J3" s="23" t="inlineStr"/>
+      <c r="H3" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K3" s="23" t="n"/>
       <c r="L3" s="64" t="inlineStr"/>
     </row>
@@ -1292,9 +1304,21 @@
 CPP will execute the job as per SI for telecom , waiting material from CPY</t>
         </is>
       </c>
-      <c r="H4" s="63" t="inlineStr"/>
-      <c r="I4" s="63" t="inlineStr"/>
-      <c r="J4" s="23" t="inlineStr"/>
+      <c r="H4" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K4" s="23" t="n"/>
       <c r="L4" s="64" t="inlineStr"/>
     </row>
@@ -1335,9 +1359,21 @@
 Cables cannot be terminated on transformer side due to gland plate issue</t>
         </is>
       </c>
-      <c r="H5" s="63" t="inlineStr"/>
-      <c r="I5" s="63" t="inlineStr"/>
-      <c r="J5" s="23" t="inlineStr"/>
+      <c r="H5" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K5" s="23" t="n"/>
       <c r="L5" s="64" t="inlineStr"/>
     </row>
@@ -1372,14 +1408,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G6" s="63" t="inlineStr"/>
+      <c r="G6" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H6" s="63" t="inlineStr">
         <is>
           <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
         </is>
       </c>
-      <c r="I6" s="63" t="inlineStr"/>
-      <c r="J6" s="23" t="inlineStr"/>
+      <c r="I6" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K6" s="23" t="n"/>
       <c r="L6" s="64" t="inlineStr"/>
     </row>
@@ -1429,7 +1477,11 @@
 PS5-71-BI-0011B-CC05 6T X 2.5 OS FL RTD 20</t>
         </is>
       </c>
-      <c r="H7" s="63" t="inlineStr"/>
+      <c r="H7" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I7" s="63" t="inlineStr">
         <is>
           <t>Piping FM &amp; Reins(TP 378 EQUIPMENT NOT AVAILABLE)</t>
@@ -1456,7 +1508,7 @@
       </c>
       <c r="C8" s="76" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -1479,9 +1531,21 @@
           <t>Due to gland plate issue of SEA-0001 we cannot terminate the cablesof F&amp;G Instruments.</t>
         </is>
       </c>
-      <c r="H8" s="63" t="inlineStr"/>
-      <c r="I8" s="63" t="inlineStr"/>
-      <c r="J8" s="23" t="inlineStr"/>
+      <c r="H8" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K8" s="23" t="n"/>
       <c r="L8" s="64" t="inlineStr"/>
     </row>
@@ -1516,14 +1580,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G9" s="63" t="inlineStr"/>
+      <c r="G9" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H9" s="63" t="inlineStr">
         <is>
           <t>all the cables cannot be laid due to pending excavation to office/building area.</t>
         </is>
       </c>
-      <c r="I9" s="63" t="inlineStr"/>
-      <c r="J9" s="23" t="inlineStr"/>
+      <c r="I9" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K9" s="23" t="n"/>
       <c r="L9" s="64" t="inlineStr"/>
     </row>
@@ -1540,7 +1616,7 @@
       </c>
       <c r="C10" s="75" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -1558,10 +1634,26 @@
           <t>14</t>
         </is>
       </c>
-      <c r="G10" s="63" t="inlineStr"/>
-      <c r="H10" s="63" t="inlineStr"/>
-      <c r="I10" s="63" t="inlineStr"/>
-      <c r="J10" s="23" t="inlineStr"/>
+      <c r="G10" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K10" s="23" t="n"/>
       <c r="L10" s="64" t="inlineStr"/>
     </row>
@@ -1578,7 +1670,7 @@
       </c>
       <c r="C11" s="76" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -1602,9 +1694,21 @@
 2) PS5-60-BI-0016D-CCO4 6T X 0.75 IS/OS FL RTD 121m</t>
         </is>
       </c>
-      <c r="H11" s="63" t="inlineStr"/>
-      <c r="I11" s="63" t="inlineStr"/>
-      <c r="J11" s="23" t="inlineStr"/>
+      <c r="H11" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K11" s="23" t="n"/>
       <c r="L11" s="64" t="inlineStr"/>
     </row>
@@ -1621,7 +1725,7 @@
       </c>
       <c r="C12" s="76" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -1639,14 +1743,26 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G12" s="63" t="inlineStr"/>
+      <c r="G12" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H12" s="63" t="inlineStr">
         <is>
           <t>PS5-61-IV-0005A/5B Not arrived.</t>
         </is>
       </c>
-      <c r="I12" s="63" t="inlineStr"/>
-      <c r="J12" s="23" t="inlineStr"/>
+      <c r="I12" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K12" s="23" t="n"/>
       <c r="L12" s="64" t="inlineStr"/>
     </row>
@@ -1687,9 +1803,21 @@
 PS5-71-BE-0005-CL04 2C+E 2.5 210m.             These cables were added in latest revision, not available.</t>
         </is>
       </c>
-      <c r="H13" s="63" t="inlineStr"/>
-      <c r="I13" s="63" t="inlineStr"/>
-      <c r="J13" s="23" t="inlineStr"/>
+      <c r="H13" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K13" s="23" t="n"/>
       <c r="L13" s="64" t="inlineStr"/>
     </row>
@@ -1729,9 +1857,21 @@
           <t>PS5-03-RDOS-1501/1502/1503 not arrived</t>
         </is>
       </c>
-      <c r="H14" s="63" t="inlineStr"/>
-      <c r="I14" s="63" t="inlineStr"/>
-      <c r="J14" s="23" t="inlineStr"/>
+      <c r="H14" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K14" s="23" t="n"/>
       <c r="L14" s="64" t="inlineStr"/>
     </row>
@@ -1771,9 +1911,21 @@
           <t>PS5-03-RDOS-1601/1602/1603 not arrived yet</t>
         </is>
       </c>
-      <c r="H15" s="63" t="inlineStr"/>
-      <c r="I15" s="63" t="inlineStr"/>
-      <c r="J15" s="23" t="inlineStr"/>
+      <c r="H15" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K15" s="23" t="n"/>
       <c r="L15" s="64" t="inlineStr"/>
     </row>
@@ -1813,9 +1965,21 @@
           <t>PS5-03-RDH-1901/1902/1903 not arrived</t>
         </is>
       </c>
-      <c r="H16" s="63" t="inlineStr"/>
-      <c r="I16" s="63" t="inlineStr"/>
-      <c r="J16" s="23" t="inlineStr"/>
+      <c r="H16" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K16" s="23" t="n"/>
       <c r="L16" s="64" t="inlineStr"/>
     </row>
@@ -1855,9 +2019,21 @@
           <t>CPP will execute the job as per SI for telecom , waiting material from CPY</t>
         </is>
       </c>
-      <c r="H17" s="63" t="inlineStr"/>
-      <c r="I17" s="63" t="inlineStr"/>
-      <c r="J17" s="23" t="inlineStr"/>
+      <c r="H17" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K17" s="23" t="n"/>
       <c r="L17" s="64" t="inlineStr"/>
     </row>
@@ -1874,7 +2050,7 @@
       </c>
       <c r="C18" s="76" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -1897,9 +2073,21 @@
           <t>6 ITRS pending due to LIT 1201/1202 (not arrived yet)</t>
         </is>
       </c>
-      <c r="H18" s="63" t="inlineStr"/>
-      <c r="I18" s="63" t="inlineStr"/>
-      <c r="J18" s="23" t="inlineStr"/>
+      <c r="H18" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I18" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K18" s="23" t="n"/>
       <c r="L18" s="64" t="inlineStr"/>
     </row>
@@ -1944,8 +2132,16 @@
           <t>Grounding cable missing 1x240mm2</t>
         </is>
       </c>
-      <c r="I19" s="63" t="inlineStr"/>
-      <c r="J19" s="23" t="inlineStr"/>
+      <c r="I19" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K19" s="23" t="n"/>
       <c r="L19" s="64" t="inlineStr"/>
     </row>
@@ -1990,8 +2186,16 @@
           <t>1x240mm2 cable not available.CPP Supply</t>
         </is>
       </c>
-      <c r="I20" s="63" t="inlineStr"/>
-      <c r="J20" s="23" t="inlineStr"/>
+      <c r="I20" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K20" s="23" t="n"/>
       <c r="L20" s="64" t="inlineStr"/>
     </row>
@@ -2006,9 +2210,9 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C21" s="75" t="inlineStr">
-        <is>
-          <t>46%</t>
+      <c r="C21" s="76" t="inlineStr">
+        <is>
+          <t>54%</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -2036,8 +2240,16 @@
           <t>PS5-60-IH-0001C-CG01 1x240mm2 grounding cable 40m</t>
         </is>
       </c>
-      <c r="I21" s="63" t="inlineStr"/>
-      <c r="J21" s="23" t="inlineStr"/>
+      <c r="I21" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K21" s="23" t="n"/>
       <c r="L21" s="64" t="inlineStr"/>
     </row>
@@ -2082,8 +2294,16 @@
           <t>PS5-60-IH-0001D-CG01 1x240mm2 grounding cable, 35m</t>
         </is>
       </c>
-      <c r="I22" s="63" t="inlineStr"/>
-      <c r="J22" s="23" t="inlineStr"/>
+      <c r="I22" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K22" s="23" t="n"/>
       <c r="L22" s="64" t="inlineStr"/>
     </row>
@@ -2100,7 +2320,7 @@
       </c>
       <c r="C23" s="76" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -2124,9 +2344,21 @@
 PS5-71-FIT-0019 not arrived.</t>
         </is>
       </c>
-      <c r="H23" s="63" t="inlineStr"/>
-      <c r="I23" s="63" t="inlineStr"/>
-      <c r="J23" s="23" t="inlineStr"/>
+      <c r="H23" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K23" s="23" t="n"/>
       <c r="L23" s="64" t="inlineStr"/>
     </row>
@@ -2143,7 +2375,7 @@
       </c>
       <c r="C24" s="76" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -2161,8 +2393,16 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G24" s="63" t="inlineStr"/>
-      <c r="H24" s="63" t="inlineStr"/>
+      <c r="G24" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I24" s="63" t="inlineStr">
         <is>
           <t>Mech(WAITING FOR ALIGNMENT TOOL)ARRAIVED-18-08-2026</t>
@@ -2212,9 +2452,21 @@
           <t>CPP will execute the job as per SI for telecom , waiting material from CPY</t>
         </is>
       </c>
-      <c r="H25" s="63" t="inlineStr"/>
-      <c r="I25" s="63" t="inlineStr"/>
-      <c r="J25" s="23" t="inlineStr"/>
+      <c r="H25" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K25" s="23" t="n"/>
       <c r="L25" s="64" t="inlineStr"/>
     </row>
@@ -2229,9 +2481,9 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C26" s="75" t="inlineStr">
-        <is>
-          <t>48%</t>
+      <c r="C26" s="76" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -2254,9 +2506,21 @@
           <t>1)Waiting delivery of CAT6A material by EACOP</t>
         </is>
       </c>
-      <c r="H26" s="63" t="inlineStr"/>
-      <c r="I26" s="63" t="inlineStr"/>
-      <c r="J26" s="23" t="inlineStr"/>
+      <c r="H26" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K26" s="23" t="n"/>
       <c r="L26" s="64" t="inlineStr"/>
     </row>
@@ -2296,9 +2560,21 @@
           <t>Waiting delivery of CAT6A material by EACOP</t>
         </is>
       </c>
-      <c r="H27" s="63" t="inlineStr"/>
-      <c r="I27" s="63" t="inlineStr"/>
-      <c r="J27" s="23" t="inlineStr"/>
+      <c r="H27" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I27" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K27" s="23" t="n"/>
       <c r="L27" s="64" t="inlineStr"/>
     </row>
@@ -2339,9 +2615,21 @@
 PS5-71-BI-0009-CC01, 175m, Cable type:6T X 2.5 IS/OS FR</t>
         </is>
       </c>
-      <c r="H28" s="63" t="inlineStr"/>
-      <c r="I28" s="63" t="inlineStr"/>
-      <c r="J28" s="23" t="inlineStr"/>
+      <c r="H28" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K28" s="23" t="n"/>
       <c r="L28" s="64" t="inlineStr"/>
     </row>
@@ -2383,9 +2671,21 @@
 PS5-71-BI-0005-CC02 Engineering Issue</t>
         </is>
       </c>
-      <c r="H29" s="63" t="inlineStr"/>
-      <c r="I29" s="63" t="inlineStr"/>
-      <c r="J29" s="23" t="inlineStr"/>
+      <c r="H29" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I29" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K29" s="23" t="n"/>
       <c r="L29" s="64" t="inlineStr"/>
     </row>
@@ -2425,9 +2725,21 @@
           <t>HVAC METERIAL ARIVED-17-08-26</t>
         </is>
       </c>
-      <c r="H30" s="63" t="inlineStr"/>
-      <c r="I30" s="63" t="inlineStr"/>
-      <c r="J30" s="23" t="inlineStr"/>
+      <c r="H30" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I30" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K30" s="23" t="n"/>
       <c r="L30" s="64" t="inlineStr"/>
     </row>
@@ -2442,9 +2754,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C31" s="76" t="inlineStr">
-        <is>
-          <t>87%</t>
+      <c r="C31" s="77" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -2467,7 +2779,11 @@
           <t>PS5-60-LIT-4301 not arrived.</t>
         </is>
       </c>
-      <c r="H31" s="63" t="inlineStr"/>
+      <c r="H31" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I31" s="63" t="inlineStr">
         <is>
           <t>Mechanical-PUMP ALIGNMENT TOOL NOT AVAILABLE-ARRAIVED-18-08-2026</t>
@@ -2494,7 +2810,7 @@
       </c>
       <c r="C32" s="76" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -2517,7 +2833,11 @@
           <t>PS5-60-LIT-4401 not arrived</t>
         </is>
       </c>
-      <c r="H32" s="63" t="inlineStr"/>
+      <c r="H32" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I32" s="63" t="inlineStr">
         <is>
           <t>Mechanical-PUMP ALIGNMENT TOOL NOT AVAILABLE-ARRAIVED-18-08-2026</t>
@@ -2572,8 +2892,16 @@
           <t>1x25mm2 cable not available.CPP Supply</t>
         </is>
       </c>
-      <c r="I33" s="63" t="inlineStr"/>
-      <c r="J33" s="23" t="inlineStr"/>
+      <c r="I33" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K33" s="23" t="n"/>
       <c r="L33" s="64" t="inlineStr"/>
     </row>
@@ -2618,8 +2946,16 @@
           <t>1x25mm2 cable not available.CPP Supply</t>
         </is>
       </c>
-      <c r="I34" s="63" t="inlineStr"/>
-      <c r="J34" s="23" t="inlineStr"/>
+      <c r="I34" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K34" s="23" t="n"/>
       <c r="L34" s="64" t="inlineStr"/>
     </row>
@@ -2664,8 +3000,16 @@
           <t>PS5-60-IN-0002C-CG01 1X25mm2 grounding cable 130m</t>
         </is>
       </c>
-      <c r="I35" s="63" t="inlineStr"/>
-      <c r="J35" s="23" t="inlineStr"/>
+      <c r="I35" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K35" s="23" t="n"/>
       <c r="L35" s="64" t="inlineStr"/>
     </row>
@@ -2710,8 +3054,16 @@
           <t>PS5-60-IN-0002D-CG01 1x25mm2 grounding cable 120m</t>
         </is>
       </c>
-      <c r="I36" s="63" t="inlineStr"/>
-      <c r="J36" s="23" t="inlineStr"/>
+      <c r="I36" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J36" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K36" s="23" t="n"/>
       <c r="L36" s="64" t="inlineStr"/>
     </row>
@@ -2728,7 +3080,7 @@
       </c>
       <c r="C37" s="76" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
@@ -2752,9 +3104,21 @@
 PS5-71-BI-0003-CC01 engineering issue.</t>
         </is>
       </c>
-      <c r="H37" s="63" t="inlineStr"/>
-      <c r="I37" s="63" t="inlineStr"/>
-      <c r="J37" s="23" t="inlineStr"/>
+      <c r="H37" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I37" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K37" s="23" t="n"/>
       <c r="L37" s="64" t="inlineStr"/>
     </row>
@@ -2771,7 +3135,7 @@
       </c>
       <c r="C38" s="77" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
@@ -2789,10 +3153,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G38" s="63" t="inlineStr"/>
-      <c r="H38" s="63" t="inlineStr"/>
-      <c r="I38" s="63" t="inlineStr"/>
-      <c r="J38" s="23" t="inlineStr"/>
+      <c r="G38" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H38" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I38" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K38" s="23" t="n"/>
       <c r="L38" s="64" t="inlineStr"/>
     </row>
@@ -2809,7 +3189,7 @@
       </c>
       <c r="C39" s="76" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
@@ -2832,9 +3212,21 @@
           <t>PS5-60-BI-0016C-CCO4 6T X 0.75 IS/OS FL RTD 131m</t>
         </is>
       </c>
-      <c r="H39" s="63" t="inlineStr"/>
-      <c r="I39" s="63" t="inlineStr"/>
-      <c r="J39" s="23" t="inlineStr"/>
+      <c r="H39" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K39" s="23" t="n"/>
       <c r="L39" s="64" t="inlineStr"/>
     </row>
@@ -2851,7 +3243,7 @@
       </c>
       <c r="C40" s="77" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
@@ -2874,7 +3266,11 @@
           <t>Cables pending due to PIT location issue, colliding with pipes</t>
         </is>
       </c>
-      <c r="H40" s="63" t="inlineStr"/>
+      <c r="H40" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I40" s="63" t="inlineStr">
         <is>
           <t>THERMAL INSULATION</t>
@@ -2901,7 +3297,7 @@
       </c>
       <c r="C41" s="77" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
@@ -2924,7 +3320,11 @@
           <t>Cables pending due to PIT location issue, colliding with pipes</t>
         </is>
       </c>
-      <c r="H41" s="63" t="inlineStr"/>
+      <c r="H41" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I41" s="63" t="inlineStr">
         <is>
           <t>THERMAL INSULATION</t>
@@ -2951,7 +3351,7 @@
       </c>
       <c r="C42" s="76" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
@@ -2974,9 +3374,21 @@
           <t>Cables pending due to PIT location issue, colliding with pipes</t>
         </is>
       </c>
-      <c r="H42" s="63" t="inlineStr"/>
-      <c r="I42" s="63" t="inlineStr"/>
-      <c r="J42" s="23" t="inlineStr"/>
+      <c r="H42" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I42" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K42" s="23" t="n"/>
       <c r="L42" s="64" t="inlineStr"/>
     </row>
@@ -3016,9 +3428,21 @@
           <t>Cables pending due to PIT location issue, colliding with pipes</t>
         </is>
       </c>
-      <c r="H43" s="63" t="inlineStr"/>
-      <c r="I43" s="63" t="inlineStr"/>
-      <c r="J43" s="23" t="inlineStr"/>
+      <c r="H43" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I43" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K43" s="23" t="n"/>
       <c r="L43" s="64" t="inlineStr"/>
     </row>
@@ -3053,14 +3477,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G44" s="63" t="inlineStr"/>
+      <c r="G44" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H44" s="63" t="inlineStr">
         <is>
           <t>lightning cannot be completed due to materials</t>
         </is>
       </c>
-      <c r="I44" s="63" t="inlineStr"/>
-      <c r="J44" s="23" t="inlineStr"/>
+      <c r="I44" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K44" s="23" t="n"/>
       <c r="L44" s="64" t="inlineStr"/>
     </row>
@@ -3077,7 +3513,7 @@
       </c>
       <c r="C45" s="77" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
@@ -3100,9 +3536,21 @@
           <t>CPP will execute the job as per SI for telecom , waiting material from CPY</t>
         </is>
       </c>
-      <c r="H45" s="63" t="inlineStr"/>
-      <c r="I45" s="63" t="inlineStr"/>
-      <c r="J45" s="23" t="inlineStr"/>
+      <c r="H45" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I45" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K45" s="23" t="n"/>
       <c r="L45" s="64" t="inlineStr"/>
     </row>
@@ -3119,7 +3567,7 @@
       </c>
       <c r="C46" s="77" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
@@ -3142,9 +3590,21 @@
           <t>CPP will execute the job as per SI for telecom , waiting material from CPY</t>
         </is>
       </c>
-      <c r="H46" s="63" t="inlineStr"/>
-      <c r="I46" s="63" t="inlineStr"/>
-      <c r="J46" s="23" t="inlineStr"/>
+      <c r="H46" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I46" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K46" s="23" t="n"/>
       <c r="L46" s="64" t="inlineStr"/>
     </row>
@@ -3161,7 +3621,7 @@
       </c>
       <c r="C47" s="76" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
@@ -3184,9 +3644,21 @@
           <t>CPP will execute the job as per SI for telecom , waiting material from CPY</t>
         </is>
       </c>
-      <c r="H47" s="63" t="inlineStr"/>
-      <c r="I47" s="63" t="inlineStr"/>
-      <c r="J47" s="23" t="inlineStr"/>
+      <c r="H47" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I47" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K47" s="23" t="n"/>
       <c r="L47" s="64" t="inlineStr"/>
     </row>
@@ -3203,7 +3675,7 @@
       </c>
       <c r="C48" s="76" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="D48" s="23" t="inlineStr">
@@ -3226,9 +3698,21 @@
           <t>CPP will execute the job as per SI for telecom , waiting material from CPY</t>
         </is>
       </c>
-      <c r="H48" s="63" t="inlineStr"/>
-      <c r="I48" s="63" t="inlineStr"/>
-      <c r="J48" s="23" t="inlineStr"/>
+      <c r="H48" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I48" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K48" s="23" t="n"/>
       <c r="L48" s="64" t="inlineStr"/>
     </row>
@@ -3243,9 +3727,9 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C49" s="75" t="inlineStr">
-        <is>
-          <t>49%</t>
+      <c r="C49" s="76" t="inlineStr">
+        <is>
+          <t>51%</t>
         </is>
       </c>
       <c r="D49" s="23" t="inlineStr">
@@ -3263,10 +3747,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G49" s="63" t="inlineStr"/>
-      <c r="H49" s="63" t="inlineStr"/>
-      <c r="I49" s="63" t="inlineStr"/>
-      <c r="J49" s="23" t="inlineStr"/>
+      <c r="G49" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H49" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I49" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J49" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K49" s="23" t="n"/>
       <c r="L49" s="64" t="inlineStr"/>
     </row>
@@ -3301,10 +3801,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G50" s="63" t="inlineStr"/>
-      <c r="H50" s="63" t="inlineStr"/>
-      <c r="I50" s="63" t="inlineStr"/>
-      <c r="J50" s="23" t="inlineStr"/>
+      <c r="G50" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H50" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I50" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K50" s="23" t="n"/>
       <c r="L50" s="64" t="inlineStr"/>
     </row>
@@ -3321,7 +3837,7 @@
       </c>
       <c r="C51" s="76" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="D51" s="23" t="inlineStr">
@@ -3339,10 +3855,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G51" s="63" t="inlineStr"/>
-      <c r="H51" s="63" t="inlineStr"/>
-      <c r="I51" s="63" t="inlineStr"/>
-      <c r="J51" s="23" t="inlineStr"/>
+      <c r="G51" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H51" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I51" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J51" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K51" s="23" t="n"/>
       <c r="L51" s="64" t="inlineStr"/>
     </row>
@@ -3377,10 +3909,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G52" s="63" t="inlineStr"/>
-      <c r="H52" s="63" t="inlineStr"/>
-      <c r="I52" s="63" t="inlineStr"/>
-      <c r="J52" s="23" t="inlineStr"/>
+      <c r="G52" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H52" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I52" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J52" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K52" s="23" t="n"/>
       <c r="L52" s="64" t="inlineStr"/>
     </row>
@@ -3415,10 +3963,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G53" s="63" t="inlineStr"/>
-      <c r="H53" s="63" t="inlineStr"/>
-      <c r="I53" s="63" t="inlineStr"/>
-      <c r="J53" s="23" t="inlineStr"/>
+      <c r="G53" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H53" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I53" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J53" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K53" s="23" t="n"/>
       <c r="L53" s="64" t="inlineStr"/>
     </row>
@@ -3453,10 +4017,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G54" s="63" t="inlineStr"/>
-      <c r="H54" s="63" t="inlineStr"/>
-      <c r="I54" s="63" t="inlineStr"/>
-      <c r="J54" s="23" t="inlineStr"/>
+      <c r="G54" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H54" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I54" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J54" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K54" s="23" t="n"/>
       <c r="L54" s="64" t="inlineStr"/>
     </row>
@@ -3473,7 +4053,7 @@
       </c>
       <c r="C55" s="76" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="D55" s="23" t="inlineStr">
@@ -3491,10 +4071,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G55" s="63" t="inlineStr"/>
-      <c r="H55" s="63" t="inlineStr"/>
-      <c r="I55" s="63" t="inlineStr"/>
-      <c r="J55" s="23" t="inlineStr"/>
+      <c r="G55" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H55" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I55" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J55" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K55" s="23" t="n"/>
       <c r="L55" s="64" t="inlineStr"/>
     </row>
@@ -3511,7 +4107,7 @@
       </c>
       <c r="C56" s="76" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="D56" s="23" t="inlineStr">
@@ -3529,10 +4125,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G56" s="63" t="inlineStr"/>
-      <c r="H56" s="63" t="inlineStr"/>
-      <c r="I56" s="63" t="inlineStr"/>
-      <c r="J56" s="23" t="inlineStr"/>
+      <c r="G56" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H56" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I56" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J56" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K56" s="23" t="n"/>
       <c r="L56" s="64" t="inlineStr"/>
     </row>
@@ -3567,10 +4179,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G57" s="63" t="inlineStr"/>
-      <c r="H57" s="63" t="inlineStr"/>
-      <c r="I57" s="63" t="inlineStr"/>
-      <c r="J57" s="23" t="inlineStr"/>
+      <c r="G57" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H57" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I57" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J57" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K57" s="23" t="n"/>
       <c r="L57" s="64" t="inlineStr"/>
     </row>
@@ -3605,10 +4233,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G58" s="63" t="inlineStr"/>
-      <c r="H58" s="63" t="inlineStr"/>
-      <c r="I58" s="63" t="inlineStr"/>
-      <c r="J58" s="23" t="inlineStr"/>
+      <c r="G58" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H58" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I58" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J58" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K58" s="23" t="n"/>
       <c r="L58" s="64" t="inlineStr"/>
     </row>
@@ -3643,10 +4287,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G59" s="63" t="inlineStr"/>
-      <c r="H59" s="63" t="inlineStr"/>
-      <c r="I59" s="63" t="inlineStr"/>
-      <c r="J59" s="23" t="inlineStr"/>
+      <c r="G59" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H59" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I59" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J59" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K59" s="23" t="n"/>
       <c r="L59" s="64" t="inlineStr"/>
     </row>
@@ -3681,10 +4341,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G60" s="63" t="inlineStr"/>
-      <c r="H60" s="63" t="inlineStr"/>
-      <c r="I60" s="63" t="inlineStr"/>
-      <c r="J60" s="23" t="inlineStr"/>
+      <c r="G60" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H60" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I60" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J60" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K60" s="23" t="n"/>
       <c r="L60" s="64" t="inlineStr"/>
     </row>
@@ -3719,10 +4395,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G61" s="63" t="inlineStr"/>
-      <c r="H61" s="63" t="inlineStr"/>
-      <c r="I61" s="63" t="inlineStr"/>
-      <c r="J61" s="23" t="inlineStr"/>
+      <c r="G61" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H61" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I61" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J61" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K61" s="23" t="n"/>
       <c r="L61" s="64" t="inlineStr"/>
     </row>
@@ -3757,10 +4449,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G62" s="63" t="inlineStr"/>
-      <c r="H62" s="63" t="inlineStr"/>
-      <c r="I62" s="63" t="inlineStr"/>
-      <c r="J62" s="23" t="inlineStr"/>
+      <c r="G62" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H62" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I62" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J62" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K62" s="23" t="n"/>
       <c r="L62" s="64" t="inlineStr"/>
     </row>
@@ -3795,10 +4503,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G63" s="63" t="inlineStr"/>
-      <c r="H63" s="63" t="inlineStr"/>
-      <c r="I63" s="63" t="inlineStr"/>
-      <c r="J63" s="23" t="inlineStr"/>
+      <c r="G63" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H63" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I63" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J63" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K63" s="23" t="n"/>
       <c r="L63" s="64" t="inlineStr"/>
     </row>
@@ -3815,7 +4539,7 @@
       </c>
       <c r="C64" s="75" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="D64" s="23" t="inlineStr">
@@ -3833,10 +4557,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G64" s="63" t="inlineStr"/>
-      <c r="H64" s="63" t="inlineStr"/>
-      <c r="I64" s="63" t="inlineStr"/>
-      <c r="J64" s="23" t="inlineStr"/>
+      <c r="G64" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H64" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I64" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J64" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K64" s="23" t="n"/>
       <c r="L64" s="64" t="inlineStr"/>
     </row>
@@ -3871,10 +4611,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G65" s="63" t="inlineStr"/>
-      <c r="H65" s="63" t="inlineStr"/>
-      <c r="I65" s="63" t="inlineStr"/>
-      <c r="J65" s="23" t="inlineStr"/>
+      <c r="G65" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H65" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I65" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J65" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K65" s="23" t="n"/>
       <c r="L65" s="64" t="inlineStr"/>
     </row>
@@ -3909,10 +4665,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G66" s="63" t="inlineStr"/>
-      <c r="H66" s="63" t="inlineStr"/>
-      <c r="I66" s="63" t="inlineStr"/>
-      <c r="J66" s="23" t="inlineStr"/>
+      <c r="G66" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H66" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I66" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J66" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K66" s="23" t="n"/>
       <c r="L66" s="64" t="inlineStr"/>
     </row>
@@ -3947,10 +4719,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G67" s="63" t="inlineStr"/>
-      <c r="H67" s="63" t="inlineStr"/>
-      <c r="I67" s="63" t="inlineStr"/>
-      <c r="J67" s="23" t="inlineStr"/>
+      <c r="G67" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H67" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I67" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J67" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K67" s="23" t="n"/>
       <c r="L67" s="64" t="inlineStr"/>
     </row>
@@ -3985,10 +4773,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G68" s="63" t="inlineStr"/>
-      <c r="H68" s="63" t="inlineStr"/>
-      <c r="I68" s="63" t="inlineStr"/>
-      <c r="J68" s="23" t="inlineStr"/>
+      <c r="G68" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H68" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I68" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J68" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K68" s="23" t="n"/>
       <c r="L68" s="64" t="inlineStr"/>
     </row>
@@ -4023,10 +4827,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G69" s="63" t="inlineStr"/>
-      <c r="H69" s="63" t="inlineStr"/>
-      <c r="I69" s="63" t="inlineStr"/>
-      <c r="J69" s="23" t="inlineStr"/>
+      <c r="G69" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H69" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I69" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J69" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K69" s="23" t="n"/>
       <c r="L69" s="64" t="inlineStr"/>
     </row>
@@ -4061,10 +4881,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G70" s="63" t="inlineStr"/>
-      <c r="H70" s="63" t="inlineStr"/>
-      <c r="I70" s="63" t="inlineStr"/>
-      <c r="J70" s="23" t="inlineStr"/>
+      <c r="G70" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H70" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I70" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J70" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K70" s="23" t="n"/>
       <c r="L70" s="64" t="inlineStr"/>
     </row>
@@ -4099,10 +4935,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G71" s="63" t="inlineStr"/>
-      <c r="H71" s="63" t="inlineStr"/>
-      <c r="I71" s="63" t="inlineStr"/>
-      <c r="J71" s="23" t="inlineStr"/>
+      <c r="G71" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H71" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I71" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J71" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K71" s="23" t="n"/>
       <c r="L71" s="64" t="inlineStr"/>
     </row>
@@ -4137,10 +4989,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G72" s="63" t="inlineStr"/>
-      <c r="H72" s="63" t="inlineStr"/>
-      <c r="I72" s="63" t="inlineStr"/>
-      <c r="J72" s="23" t="inlineStr"/>
+      <c r="G72" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H72" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I72" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J72" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K72" s="23" t="n"/>
       <c r="L72" s="64" t="inlineStr"/>
     </row>
@@ -4175,10 +5043,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G73" s="63" t="inlineStr"/>
-      <c r="H73" s="63" t="inlineStr"/>
-      <c r="I73" s="63" t="inlineStr"/>
-      <c r="J73" s="23" t="inlineStr"/>
+      <c r="G73" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H73" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I73" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J73" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K73" s="23" t="n"/>
       <c r="L73" s="64" t="inlineStr"/>
     </row>
@@ -4213,10 +5097,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G74" s="63" t="inlineStr"/>
-      <c r="H74" s="63" t="inlineStr"/>
-      <c r="I74" s="63" t="inlineStr"/>
-      <c r="J74" s="23" t="inlineStr"/>
+      <c r="G74" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H74" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I74" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J74" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K74" s="23" t="n"/>
       <c r="L74" s="64" t="inlineStr"/>
     </row>
@@ -4251,10 +5151,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G75" s="63" t="inlineStr"/>
-      <c r="H75" s="63" t="inlineStr"/>
-      <c r="I75" s="63" t="inlineStr"/>
-      <c r="J75" s="23" t="inlineStr"/>
+      <c r="G75" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H75" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I75" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J75" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K75" s="23" t="n"/>
       <c r="L75" s="64" t="inlineStr"/>
     </row>
@@ -4317,10 +5233,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G77" s="63" t="inlineStr"/>
-      <c r="H77" s="63" t="inlineStr"/>
-      <c r="I77" s="63" t="inlineStr"/>
-      <c r="J77" s="23" t="inlineStr"/>
+      <c r="G77" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H77" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I77" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J77" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K77" s="23" t="n"/>
       <c r="L77" s="64" t="inlineStr"/>
     </row>
@@ -4355,10 +5287,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G78" s="63" t="inlineStr"/>
-      <c r="H78" s="63" t="inlineStr"/>
-      <c r="I78" s="63" t="inlineStr"/>
-      <c r="J78" s="23" t="inlineStr"/>
+      <c r="G78" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H78" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I78" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J78" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K78" s="23" t="n"/>
       <c r="L78" s="64" t="inlineStr"/>
     </row>
@@ -4421,10 +5369,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G80" s="63" t="inlineStr"/>
-      <c r="H80" s="63" t="inlineStr"/>
-      <c r="I80" s="63" t="inlineStr"/>
-      <c r="J80" s="23" t="inlineStr"/>
+      <c r="G80" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H80" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I80" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J80" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K80" s="23" t="n"/>
       <c r="L80" s="64" t="inlineStr"/>
     </row>
@@ -4543,10 +5507,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G84" s="63" t="inlineStr"/>
-      <c r="H84" s="63" t="inlineStr"/>
-      <c r="I84" s="63" t="inlineStr"/>
-      <c r="J84" s="23" t="inlineStr"/>
+      <c r="G84" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H84" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I84" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J84" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K84" s="23" t="n"/>
       <c r="L84" s="64" t="inlineStr"/>
     </row>
@@ -4581,10 +5561,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G85" s="63" t="inlineStr"/>
-      <c r="H85" s="63" t="inlineStr"/>
-      <c r="I85" s="63" t="inlineStr"/>
-      <c r="J85" s="23" t="inlineStr"/>
+      <c r="G85" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H85" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I85" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J85" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K85" s="23" t="n"/>
       <c r="L85" s="64" t="inlineStr"/>
     </row>
@@ -4647,10 +5643,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G87" s="63" t="inlineStr"/>
-      <c r="H87" s="63" t="inlineStr"/>
-      <c r="I87" s="63" t="inlineStr"/>
-      <c r="J87" s="23" t="inlineStr"/>
+      <c r="G87" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H87" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I87" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J87" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K87" s="23" t="n"/>
       <c r="L87" s="64" t="inlineStr"/>
     </row>
@@ -4685,10 +5697,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G88" s="63" t="inlineStr"/>
-      <c r="H88" s="63" t="inlineStr"/>
-      <c r="I88" s="63" t="inlineStr"/>
-      <c r="J88" s="23" t="inlineStr"/>
+      <c r="G88" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H88" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I88" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J88" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K88" s="23" t="n"/>
       <c r="L88" s="64" t="inlineStr"/>
     </row>
@@ -4723,10 +5751,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G89" s="63" t="inlineStr"/>
-      <c r="H89" s="63" t="inlineStr"/>
-      <c r="I89" s="63" t="inlineStr"/>
-      <c r="J89" s="23" t="inlineStr"/>
+      <c r="G89" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H89" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I89" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J89" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K89" s="23" t="n"/>
       <c r="L89" s="64" t="inlineStr"/>
     </row>
@@ -4761,10 +5805,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G90" s="63" t="inlineStr"/>
-      <c r="H90" s="63" t="inlineStr"/>
-      <c r="I90" s="63" t="inlineStr"/>
-      <c r="J90" s="23" t="inlineStr"/>
+      <c r="G90" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H90" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I90" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J90" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K90" s="23" t="n"/>
       <c r="L90" s="64" t="inlineStr"/>
     </row>
@@ -4799,10 +5859,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G91" s="63" t="inlineStr"/>
-      <c r="H91" s="63" t="inlineStr"/>
-      <c r="I91" s="63" t="inlineStr"/>
-      <c r="J91" s="23" t="inlineStr"/>
+      <c r="G91" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H91" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I91" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J91" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K91" s="23" t="n"/>
       <c r="L91" s="64" t="inlineStr"/>
     </row>
@@ -4837,10 +5913,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G92" s="63" t="inlineStr"/>
-      <c r="H92" s="63" t="inlineStr"/>
-      <c r="I92" s="63" t="inlineStr"/>
-      <c r="J92" s="23" t="inlineStr"/>
+      <c r="G92" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H92" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I92" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J92" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K92" s="23" t="n"/>
       <c r="L92" s="64" t="inlineStr"/>
     </row>
@@ -4931,10 +6023,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G95" s="63" t="inlineStr"/>
-      <c r="H95" s="63" t="inlineStr"/>
-      <c r="I95" s="63" t="inlineStr"/>
-      <c r="J95" s="23" t="inlineStr"/>
+      <c r="G95" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H95" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I95" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J95" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K95" s="23" t="n"/>
       <c r="L95" s="64" t="inlineStr"/>
     </row>
@@ -4969,10 +6077,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G96" s="63" t="inlineStr"/>
-      <c r="H96" s="63" t="inlineStr"/>
-      <c r="I96" s="63" t="inlineStr"/>
-      <c r="J96" s="23" t="inlineStr"/>
+      <c r="G96" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H96" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I96" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J96" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K96" s="23" t="n"/>
       <c r="L96" s="64" t="inlineStr"/>
     </row>
@@ -5007,10 +6131,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G97" s="63" t="inlineStr"/>
-      <c r="H97" s="63" t="inlineStr"/>
-      <c r="I97" s="63" t="inlineStr"/>
-      <c r="J97" s="23" t="inlineStr"/>
+      <c r="G97" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H97" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I97" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J97" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K97" s="23" t="n"/>
       <c r="L97" s="64" t="inlineStr"/>
     </row>
@@ -5045,10 +6185,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G98" s="63" t="inlineStr"/>
-      <c r="H98" s="63" t="inlineStr"/>
-      <c r="I98" s="63" t="inlineStr"/>
-      <c r="J98" s="23" t="inlineStr"/>
+      <c r="G98" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H98" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I98" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J98" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K98" s="23" t="n"/>
       <c r="L98" s="64" t="inlineStr"/>
     </row>
@@ -5083,10 +6239,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G99" s="63" t="inlineStr"/>
-      <c r="H99" s="63" t="inlineStr"/>
-      <c r="I99" s="63" t="inlineStr"/>
-      <c r="J99" s="23" t="inlineStr"/>
+      <c r="G99" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H99" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I99" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J99" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K99" s="23" t="n"/>
       <c r="L99" s="64" t="inlineStr"/>
     </row>
@@ -5121,10 +6293,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G100" s="63" t="inlineStr"/>
-      <c r="H100" s="63" t="inlineStr"/>
-      <c r="I100" s="63" t="inlineStr"/>
-      <c r="J100" s="23" t="inlineStr"/>
+      <c r="G100" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H100" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I100" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J100" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K100" s="23" t="n"/>
       <c r="L100" s="64" t="inlineStr"/>
     </row>
@@ -5159,10 +6347,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G101" s="63" t="inlineStr"/>
-      <c r="H101" s="63" t="inlineStr"/>
-      <c r="I101" s="63" t="inlineStr"/>
-      <c r="J101" s="23" t="inlineStr"/>
+      <c r="G101" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H101" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I101" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J101" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K101" s="23" t="n"/>
       <c r="L101" s="64" t="inlineStr"/>
     </row>
@@ -5225,10 +6429,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G103" s="63" t="inlineStr"/>
-      <c r="H103" s="63" t="inlineStr"/>
-      <c r="I103" s="63" t="inlineStr"/>
-      <c r="J103" s="23" t="inlineStr"/>
+      <c r="G103" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H103" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I103" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J103" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K103" s="23" t="n"/>
       <c r="L103" s="64" t="inlineStr"/>
     </row>
@@ -5263,10 +6483,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G104" s="63" t="inlineStr"/>
-      <c r="H104" s="63" t="inlineStr"/>
-      <c r="I104" s="63" t="inlineStr"/>
-      <c r="J104" s="23" t="inlineStr"/>
+      <c r="G104" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H104" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I104" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J104" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K104" s="23" t="n"/>
       <c r="L104" s="64" t="inlineStr"/>
     </row>
@@ -5301,10 +6537,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G105" s="63" t="inlineStr"/>
-      <c r="H105" s="63" t="inlineStr"/>
-      <c r="I105" s="63" t="inlineStr"/>
-      <c r="J105" s="23" t="inlineStr"/>
+      <c r="G105" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H105" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I105" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J105" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K105" s="23" t="n"/>
       <c r="L105" s="64" t="inlineStr"/>
     </row>
@@ -5367,10 +6619,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G107" s="63" t="inlineStr"/>
-      <c r="H107" s="63" t="inlineStr"/>
-      <c r="I107" s="63" t="inlineStr"/>
-      <c r="J107" s="23" t="inlineStr"/>
+      <c r="G107" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H107" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I107" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J107" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K107" s="23" t="n"/>
       <c r="L107" s="64" t="inlineStr"/>
     </row>
@@ -5405,10 +6673,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G108" s="63" t="inlineStr"/>
-      <c r="H108" s="63" t="inlineStr"/>
-      <c r="I108" s="63" t="inlineStr"/>
-      <c r="J108" s="23" t="inlineStr"/>
+      <c r="G108" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H108" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I108" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J108" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K108" s="23" t="n"/>
       <c r="L108" s="64" t="inlineStr"/>
     </row>
@@ -5443,10 +6727,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G109" s="63" t="inlineStr"/>
-      <c r="H109" s="63" t="inlineStr"/>
-      <c r="I109" s="63" t="inlineStr"/>
-      <c r="J109" s="23" t="inlineStr"/>
+      <c r="G109" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H109" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I109" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J109" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K109" s="23" t="n"/>
       <c r="L109" s="64" t="inlineStr"/>
     </row>
@@ -5537,10 +6837,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G112" s="63" t="inlineStr"/>
-      <c r="H112" s="63" t="inlineStr"/>
-      <c r="I112" s="63" t="inlineStr"/>
-      <c r="J112" s="23" t="inlineStr"/>
+      <c r="G112" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H112" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I112" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J112" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K112" s="23" t="n"/>
       <c r="L112" s="64" t="inlineStr"/>
     </row>
@@ -5575,10 +6891,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G113" s="63" t="inlineStr"/>
-      <c r="H113" s="63" t="inlineStr"/>
-      <c r="I113" s="63" t="inlineStr"/>
-      <c r="J113" s="23" t="inlineStr"/>
+      <c r="G113" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H113" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I113" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J113" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K113" s="23" t="n"/>
       <c r="L113" s="64" t="inlineStr"/>
     </row>
@@ -5669,10 +7001,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G116" s="63" t="inlineStr"/>
-      <c r="H116" s="63" t="inlineStr"/>
-      <c r="I116" s="63" t="inlineStr"/>
-      <c r="J116" s="23" t="inlineStr"/>
+      <c r="G116" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H116" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I116" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J116" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K116" s="23" t="n"/>
       <c r="L116" s="64" t="inlineStr"/>
     </row>
@@ -5707,10 +7055,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G117" s="63" t="inlineStr"/>
-      <c r="H117" s="63" t="inlineStr"/>
-      <c r="I117" s="63" t="inlineStr"/>
-      <c r="J117" s="23" t="inlineStr"/>
+      <c r="G117" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H117" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I117" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J117" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K117" s="23" t="n"/>
       <c r="L117" s="64" t="inlineStr"/>
     </row>
@@ -5745,10 +7109,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G118" s="63" t="inlineStr"/>
-      <c r="H118" s="63" t="inlineStr"/>
-      <c r="I118" s="63" t="inlineStr"/>
-      <c r="J118" s="23" t="inlineStr"/>
+      <c r="G118" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H118" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I118" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J118" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K118" s="23" t="n"/>
       <c r="L118" s="64" t="inlineStr"/>
     </row>
@@ -5783,10 +7163,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G119" s="63" t="inlineStr"/>
-      <c r="H119" s="63" t="inlineStr"/>
-      <c r="I119" s="63" t="inlineStr"/>
-      <c r="J119" s="23" t="inlineStr"/>
+      <c r="G119" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H119" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I119" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J119" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K119" s="23" t="n"/>
       <c r="L119" s="64" t="inlineStr"/>
     </row>
@@ -5821,10 +7217,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G120" s="63" t="inlineStr"/>
-      <c r="H120" s="63" t="inlineStr"/>
-      <c r="I120" s="63" t="inlineStr"/>
-      <c r="J120" s="23" t="inlineStr"/>
+      <c r="G120" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H120" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I120" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J120" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K120" s="23" t="n"/>
       <c r="L120" s="64" t="inlineStr"/>
     </row>
@@ -5887,10 +7299,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G122" s="63" t="inlineStr"/>
-      <c r="H122" s="63" t="inlineStr"/>
-      <c r="I122" s="63" t="inlineStr"/>
-      <c r="J122" s="23" t="inlineStr"/>
+      <c r="G122" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H122" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I122" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J122" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K122" s="23" t="n"/>
       <c r="L122" s="64" t="inlineStr"/>
     </row>
@@ -5925,10 +7353,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G123" s="63" t="inlineStr"/>
-      <c r="H123" s="63" t="inlineStr"/>
-      <c r="I123" s="63" t="inlineStr"/>
-      <c r="J123" s="23" t="inlineStr"/>
+      <c r="G123" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H123" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I123" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J123" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K123" s="23" t="n"/>
       <c r="L123" s="64" t="inlineStr"/>
     </row>
@@ -5963,10 +7407,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G124" s="63" t="inlineStr"/>
-      <c r="H124" s="63" t="inlineStr"/>
-      <c r="I124" s="63" t="inlineStr"/>
-      <c r="J124" s="23" t="inlineStr"/>
+      <c r="G124" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H124" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I124" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J124" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K124" s="23" t="n"/>
       <c r="L124" s="64" t="inlineStr"/>
     </row>
@@ -6001,10 +7461,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G125" s="63" t="inlineStr"/>
-      <c r="H125" s="63" t="inlineStr"/>
-      <c r="I125" s="63" t="inlineStr"/>
-      <c r="J125" s="23" t="inlineStr"/>
+      <c r="G125" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H125" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I125" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J125" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K125" s="23" t="n"/>
       <c r="L125" s="64" t="inlineStr"/>
     </row>
@@ -6039,10 +7515,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G126" s="63" t="inlineStr"/>
-      <c r="H126" s="63" t="inlineStr"/>
-      <c r="I126" s="63" t="inlineStr"/>
-      <c r="J126" s="23" t="inlineStr"/>
+      <c r="G126" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H126" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I126" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J126" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K126" s="23" t="n"/>
       <c r="L126" s="64" t="inlineStr"/>
     </row>
@@ -6077,10 +7569,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G127" s="63" t="inlineStr"/>
-      <c r="H127" s="63" t="inlineStr"/>
-      <c r="I127" s="63" t="inlineStr"/>
-      <c r="J127" s="23" t="inlineStr"/>
+      <c r="G127" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H127" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I127" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J127" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K127" s="23" t="n"/>
       <c r="L127" s="64" t="inlineStr"/>
     </row>
@@ -6115,10 +7623,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G128" s="63" t="inlineStr"/>
-      <c r="H128" s="63" t="inlineStr"/>
-      <c r="I128" s="63" t="inlineStr"/>
-      <c r="J128" s="23" t="inlineStr"/>
+      <c r="G128" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H128" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I128" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J128" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K128" s="23" t="n"/>
       <c r="L128" s="64" t="inlineStr"/>
     </row>
@@ -6153,10 +7677,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G129" s="63" t="inlineStr"/>
-      <c r="H129" s="63" t="inlineStr"/>
-      <c r="I129" s="63" t="inlineStr"/>
-      <c r="J129" s="23" t="inlineStr"/>
+      <c r="G129" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H129" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I129" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J129" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K129" s="23" t="n"/>
       <c r="L129" s="64" t="inlineStr"/>
     </row>
@@ -6191,10 +7731,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G130" s="63" t="inlineStr"/>
-      <c r="H130" s="63" t="inlineStr"/>
-      <c r="I130" s="63" t="inlineStr"/>
-      <c r="J130" s="23" t="inlineStr"/>
+      <c r="G130" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H130" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I130" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J130" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K130" s="23" t="n"/>
       <c r="L130" s="64" t="inlineStr"/>
     </row>
@@ -6211,7 +7767,7 @@
       </c>
       <c r="C131" s="76" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="D131" s="23" t="inlineStr">
@@ -6229,10 +7785,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G131" s="63" t="inlineStr"/>
-      <c r="H131" s="63" t="inlineStr"/>
-      <c r="I131" s="63" t="inlineStr"/>
-      <c r="J131" s="23" t="inlineStr"/>
+      <c r="G131" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H131" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I131" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J131" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K131" s="23" t="n"/>
       <c r="L131" s="64" t="inlineStr"/>
     </row>
@@ -6267,10 +7839,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G132" s="63" t="inlineStr"/>
-      <c r="H132" s="63" t="inlineStr"/>
-      <c r="I132" s="63" t="inlineStr"/>
-      <c r="J132" s="23" t="inlineStr"/>
+      <c r="G132" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H132" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I132" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J132" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K132" s="23" t="n"/>
       <c r="L132" s="64" t="inlineStr"/>
     </row>
@@ -6305,10 +7893,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G133" s="63" t="inlineStr"/>
-      <c r="H133" s="63" t="inlineStr"/>
-      <c r="I133" s="63" t="inlineStr"/>
-      <c r="J133" s="23" t="inlineStr"/>
+      <c r="G133" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H133" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I133" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J133" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K133" s="23" t="n"/>
       <c r="L133" s="64" t="inlineStr"/>
     </row>
@@ -6343,10 +7947,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G134" s="63" t="inlineStr"/>
-      <c r="H134" s="63" t="inlineStr"/>
-      <c r="I134" s="63" t="inlineStr"/>
-      <c r="J134" s="23" t="inlineStr"/>
+      <c r="G134" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H134" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I134" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J134" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K134" s="23" t="n"/>
       <c r="L134" s="64" t="inlineStr"/>
     </row>
@@ -6381,10 +8001,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G135" s="63" t="inlineStr"/>
-      <c r="H135" s="63" t="inlineStr"/>
-      <c r="I135" s="63" t="inlineStr"/>
-      <c r="J135" s="23" t="inlineStr"/>
+      <c r="G135" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H135" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I135" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J135" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K135" s="23" t="n"/>
       <c r="L135" s="64" t="inlineStr"/>
     </row>
@@ -6419,10 +8055,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G136" s="63" t="inlineStr"/>
-      <c r="H136" s="63" t="inlineStr"/>
-      <c r="I136" s="63" t="inlineStr"/>
-      <c r="J136" s="23" t="inlineStr"/>
+      <c r="G136" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H136" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I136" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J136" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K136" s="23" t="n"/>
       <c r="L136" s="64" t="inlineStr"/>
     </row>
@@ -6457,10 +8109,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G137" s="63" t="inlineStr"/>
-      <c r="H137" s="63" t="inlineStr"/>
-      <c r="I137" s="63" t="inlineStr"/>
-      <c r="J137" s="23" t="inlineStr"/>
+      <c r="G137" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H137" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I137" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J137" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K137" s="23" t="n"/>
       <c r="L137" s="64" t="inlineStr"/>
     </row>
@@ -6495,10 +8163,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G138" s="63" t="inlineStr"/>
-      <c r="H138" s="63" t="inlineStr"/>
-      <c r="I138" s="63" t="inlineStr"/>
-      <c r="J138" s="23" t="inlineStr"/>
+      <c r="G138" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H138" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I138" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J138" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K138" s="23" t="n"/>
       <c r="L138" s="64" t="inlineStr"/>
     </row>
@@ -6533,10 +8217,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G139" s="63" t="inlineStr"/>
-      <c r="H139" s="63" t="inlineStr"/>
-      <c r="I139" s="63" t="inlineStr"/>
-      <c r="J139" s="23" t="inlineStr"/>
+      <c r="G139" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H139" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I139" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J139" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K139" s="23" t="n"/>
       <c r="L139" s="64" t="inlineStr"/>
     </row>
@@ -6571,10 +8271,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G140" s="63" t="inlineStr"/>
-      <c r="H140" s="63" t="inlineStr"/>
-      <c r="I140" s="63" t="inlineStr"/>
-      <c r="J140" s="23" t="inlineStr"/>
+      <c r="G140" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H140" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I140" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J140" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K140" s="23" t="n"/>
       <c r="L140" s="64" t="inlineStr"/>
     </row>
@@ -6609,10 +8325,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G141" s="63" t="inlineStr"/>
-      <c r="H141" s="63" t="inlineStr"/>
-      <c r="I141" s="63" t="inlineStr"/>
-      <c r="J141" s="23" t="inlineStr"/>
+      <c r="G141" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H141" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I141" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J141" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K141" s="23" t="n"/>
       <c r="L141" s="64" t="inlineStr"/>
     </row>
@@ -6647,10 +8379,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G142" s="63" t="inlineStr"/>
-      <c r="H142" s="63" t="inlineStr"/>
-      <c r="I142" s="63" t="inlineStr"/>
-      <c r="J142" s="23" t="inlineStr"/>
+      <c r="G142" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H142" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I142" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J142" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K142" s="23" t="n"/>
       <c r="L142" s="64" t="inlineStr"/>
     </row>
@@ -6685,10 +8433,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G143" s="63" t="inlineStr"/>
-      <c r="H143" s="63" t="inlineStr"/>
-      <c r="I143" s="63" t="inlineStr"/>
-      <c r="J143" s="23" t="inlineStr"/>
+      <c r="G143" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H143" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I143" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J143" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K143" s="23" t="n"/>
       <c r="L143" s="64" t="inlineStr"/>
     </row>
@@ -6723,10 +8487,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G144" s="63" t="inlineStr"/>
-      <c r="H144" s="63" t="inlineStr"/>
-      <c r="I144" s="63" t="inlineStr"/>
-      <c r="J144" s="23" t="inlineStr"/>
+      <c r="G144" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H144" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I144" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J144" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K144" s="23" t="n"/>
       <c r="L144" s="64" t="inlineStr"/>
     </row>
@@ -6761,10 +8541,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G145" s="63" t="inlineStr"/>
-      <c r="H145" s="63" t="inlineStr"/>
-      <c r="I145" s="63" t="inlineStr"/>
-      <c r="J145" s="23" t="inlineStr"/>
+      <c r="G145" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H145" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I145" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J145" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K145" s="23" t="n"/>
       <c r="L145" s="64" t="inlineStr"/>
     </row>
@@ -6799,10 +8595,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G146" s="63" t="inlineStr"/>
-      <c r="H146" s="63" t="inlineStr"/>
-      <c r="I146" s="63" t="inlineStr"/>
-      <c r="J146" s="23" t="inlineStr"/>
+      <c r="G146" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H146" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I146" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J146" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K146" s="23" t="n"/>
       <c r="L146" s="64" t="inlineStr"/>
     </row>
@@ -6837,10 +8649,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G147" s="63" t="inlineStr"/>
-      <c r="H147" s="63" t="inlineStr"/>
-      <c r="I147" s="63" t="inlineStr"/>
-      <c r="J147" s="23" t="inlineStr"/>
+      <c r="G147" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H147" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I147" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J147" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K147" s="23" t="n"/>
       <c r="L147" s="64" t="inlineStr"/>
     </row>
@@ -6875,10 +8703,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G148" s="63" t="inlineStr"/>
-      <c r="H148" s="63" t="inlineStr"/>
-      <c r="I148" s="63" t="inlineStr"/>
-      <c r="J148" s="23" t="inlineStr"/>
+      <c r="G148" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H148" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I148" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J148" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K148" s="23" t="n"/>
       <c r="L148" s="64" t="inlineStr"/>
     </row>
@@ -6913,10 +8757,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G149" s="63" t="inlineStr"/>
-      <c r="H149" s="63" t="inlineStr"/>
-      <c r="I149" s="63" t="inlineStr"/>
-      <c r="J149" s="23" t="inlineStr"/>
+      <c r="G149" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H149" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I149" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J149" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K149" s="23" t="n"/>
       <c r="L149" s="64" t="inlineStr"/>
     </row>
@@ -6951,10 +8811,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G150" s="63" t="inlineStr"/>
-      <c r="H150" s="63" t="inlineStr"/>
-      <c r="I150" s="63" t="inlineStr"/>
-      <c r="J150" s="23" t="inlineStr"/>
+      <c r="G150" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H150" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I150" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J150" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K150" s="23" t="n"/>
       <c r="L150" s="64" t="inlineStr"/>
     </row>
@@ -6989,10 +8865,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G151" s="63" t="inlineStr"/>
-      <c r="H151" s="63" t="inlineStr"/>
-      <c r="I151" s="63" t="inlineStr"/>
-      <c r="J151" s="23" t="inlineStr"/>
+      <c r="G151" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H151" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I151" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J151" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K151" s="23" t="n"/>
       <c r="L151" s="64" t="inlineStr"/>
     </row>
@@ -7027,10 +8919,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G152" s="63" t="inlineStr"/>
-      <c r="H152" s="63" t="inlineStr"/>
-      <c r="I152" s="63" t="inlineStr"/>
-      <c r="J152" s="23" t="inlineStr"/>
+      <c r="G152" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H152" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I152" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J152" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K152" s="23" t="n"/>
       <c r="L152" s="64" t="inlineStr"/>
     </row>
@@ -7065,10 +8973,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G153" s="63" t="inlineStr"/>
-      <c r="H153" s="63" t="inlineStr"/>
-      <c r="I153" s="63" t="inlineStr"/>
-      <c r="J153" s="23" t="inlineStr"/>
+      <c r="G153" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H153" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I153" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J153" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K153" s="23" t="n"/>
       <c r="L153" s="64" t="inlineStr"/>
     </row>
@@ -7103,10 +9027,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G154" s="63" t="inlineStr"/>
-      <c r="H154" s="63" t="inlineStr"/>
-      <c r="I154" s="63" t="inlineStr"/>
-      <c r="J154" s="23" t="inlineStr"/>
+      <c r="G154" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H154" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I154" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J154" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K154" s="23" t="n"/>
       <c r="L154" s="64" t="inlineStr"/>
     </row>
@@ -7123,7 +9063,7 @@
       </c>
       <c r="C155" s="77" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="D155" s="23" t="inlineStr">
@@ -7141,10 +9081,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G155" s="63" t="inlineStr"/>
-      <c r="H155" s="63" t="inlineStr"/>
-      <c r="I155" s="63" t="inlineStr"/>
-      <c r="J155" s="23" t="inlineStr"/>
+      <c r="G155" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H155" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I155" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J155" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K155" s="23" t="n"/>
       <c r="L155" s="64" t="inlineStr"/>
     </row>
@@ -7179,10 +9135,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G156" s="63" t="inlineStr"/>
-      <c r="H156" s="63" t="inlineStr"/>
-      <c r="I156" s="63" t="inlineStr"/>
-      <c r="J156" s="23" t="inlineStr"/>
+      <c r="G156" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H156" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I156" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J156" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K156" s="23" t="n"/>
       <c r="L156" s="64" t="inlineStr"/>
     </row>
@@ -7217,10 +9189,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G157" s="63" t="inlineStr"/>
-      <c r="H157" s="63" t="inlineStr"/>
-      <c r="I157" s="63" t="inlineStr"/>
-      <c r="J157" s="23" t="inlineStr"/>
+      <c r="G157" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H157" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I157" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J157" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K157" s="23" t="n"/>
       <c r="L157" s="64" t="inlineStr"/>
     </row>
@@ -7255,10 +9243,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G158" s="63" t="inlineStr"/>
-      <c r="H158" s="63" t="inlineStr"/>
-      <c r="I158" s="63" t="inlineStr"/>
-      <c r="J158" s="23" t="inlineStr"/>
+      <c r="G158" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H158" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I158" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J158" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K158" s="23" t="n"/>
       <c r="L158" s="64" t="inlineStr"/>
     </row>
@@ -7293,10 +9297,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G159" s="63" t="inlineStr"/>
-      <c r="H159" s="63" t="inlineStr"/>
-      <c r="I159" s="63" t="inlineStr"/>
-      <c r="J159" s="23" t="inlineStr"/>
+      <c r="G159" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H159" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I159" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J159" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K159" s="23" t="n"/>
       <c r="L159" s="64" t="inlineStr"/>
     </row>
@@ -7331,10 +9351,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G160" s="63" t="inlineStr"/>
-      <c r="H160" s="63" t="inlineStr"/>
-      <c r="I160" s="63" t="inlineStr"/>
-      <c r="J160" s="23" t="inlineStr"/>
+      <c r="G160" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H160" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I160" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J160" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K160" s="23" t="n"/>
       <c r="L160" s="64" t="inlineStr"/>
     </row>
@@ -7369,10 +9405,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G161" s="63" t="inlineStr"/>
-      <c r="H161" s="63" t="inlineStr"/>
-      <c r="I161" s="63" t="inlineStr"/>
-      <c r="J161" s="23" t="inlineStr"/>
+      <c r="G161" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H161" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I161" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J161" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K161" s="23" t="n"/>
       <c r="L161" s="64" t="inlineStr"/>
     </row>
@@ -7407,10 +9459,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G162" s="63" t="inlineStr"/>
-      <c r="H162" s="63" t="inlineStr"/>
-      <c r="I162" s="63" t="inlineStr"/>
-      <c r="J162" s="23" t="inlineStr"/>
+      <c r="G162" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H162" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I162" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J162" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K162" s="23" t="n"/>
       <c r="L162" s="64" t="inlineStr"/>
     </row>
@@ -7445,10 +9513,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G163" s="63" t="inlineStr"/>
-      <c r="H163" s="63" t="inlineStr"/>
-      <c r="I163" s="63" t="inlineStr"/>
-      <c r="J163" s="23" t="inlineStr"/>
+      <c r="G163" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H163" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I163" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J163" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K163" s="23" t="n"/>
       <c r="L163" s="64" t="inlineStr"/>
     </row>
@@ -7483,10 +9567,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G164" s="63" t="inlineStr"/>
-      <c r="H164" s="63" t="inlineStr"/>
-      <c r="I164" s="63" t="inlineStr"/>
-      <c r="J164" s="23" t="inlineStr"/>
+      <c r="G164" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H164" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I164" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J164" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K164" s="23" t="n"/>
       <c r="L164" s="64" t="inlineStr"/>
     </row>
@@ -7503,7 +9603,7 @@
       </c>
       <c r="C165" s="76" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D165" s="23" t="inlineStr">
@@ -7521,10 +9621,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G165" s="63" t="inlineStr"/>
-      <c r="H165" s="63" t="inlineStr"/>
-      <c r="I165" s="63" t="inlineStr"/>
-      <c r="J165" s="23" t="inlineStr"/>
+      <c r="G165" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H165" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I165" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J165" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K165" s="23" t="n"/>
       <c r="L165" s="64" t="inlineStr"/>
     </row>
@@ -7559,10 +9675,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G166" s="63" t="inlineStr"/>
-      <c r="H166" s="63" t="inlineStr"/>
-      <c r="I166" s="63" t="inlineStr"/>
-      <c r="J166" s="23" t="inlineStr"/>
+      <c r="G166" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H166" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I166" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J166" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K166" s="23" t="n"/>
       <c r="L166" s="64" t="inlineStr"/>
     </row>
@@ -7579,7 +9711,7 @@
       </c>
       <c r="C167" s="77" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D167" s="23" t="inlineStr">
@@ -7597,10 +9729,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G167" s="63" t="inlineStr"/>
-      <c r="H167" s="63" t="inlineStr"/>
-      <c r="I167" s="63" t="inlineStr"/>
-      <c r="J167" s="23" t="inlineStr"/>
+      <c r="G167" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H167" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I167" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J167" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K167" s="23" t="n"/>
       <c r="L167" s="64" t="inlineStr"/>
     </row>
@@ -7635,10 +9783,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G168" s="63" t="inlineStr"/>
-      <c r="H168" s="63" t="inlineStr"/>
-      <c r="I168" s="63" t="inlineStr"/>
-      <c r="J168" s="23" t="inlineStr"/>
+      <c r="G168" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H168" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I168" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J168" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K168" s="23" t="n"/>
       <c r="L168" s="64" t="inlineStr"/>
     </row>
@@ -7673,10 +9837,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G169" s="63" t="inlineStr"/>
-      <c r="H169" s="63" t="inlineStr"/>
-      <c r="I169" s="63" t="inlineStr"/>
-      <c r="J169" s="23" t="inlineStr"/>
+      <c r="G169" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H169" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I169" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J169" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K169" s="23" t="n"/>
       <c r="L169" s="64" t="inlineStr"/>
     </row>
@@ -7711,10 +9891,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G170" s="63" t="inlineStr"/>
-      <c r="H170" s="63" t="inlineStr"/>
-      <c r="I170" s="63" t="inlineStr"/>
-      <c r="J170" s="23" t="inlineStr"/>
+      <c r="G170" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H170" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I170" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J170" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K170" s="23" t="n"/>
       <c r="L170" s="64" t="inlineStr"/>
     </row>
@@ -7749,10 +9945,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G171" s="63" t="inlineStr"/>
-      <c r="H171" s="63" t="inlineStr"/>
-      <c r="I171" s="63" t="inlineStr"/>
-      <c r="J171" s="23" t="inlineStr"/>
+      <c r="G171" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H171" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I171" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J171" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K171" s="23" t="n"/>
       <c r="L171" s="64" t="inlineStr"/>
     </row>
@@ -7787,10 +9999,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G172" s="63" t="inlineStr"/>
-      <c r="H172" s="63" t="inlineStr"/>
-      <c r="I172" s="63" t="inlineStr"/>
-      <c r="J172" s="23" t="inlineStr"/>
+      <c r="G172" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H172" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I172" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J172" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K172" s="23" t="n"/>
       <c r="L172" s="64" t="inlineStr"/>
     </row>
@@ -7825,10 +10053,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G173" s="63" t="inlineStr"/>
-      <c r="H173" s="63" t="inlineStr"/>
-      <c r="I173" s="63" t="inlineStr"/>
-      <c r="J173" s="23" t="inlineStr"/>
+      <c r="G173" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H173" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I173" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J173" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K173" s="23" t="n"/>
       <c r="L173" s="64" t="inlineStr"/>
     </row>
@@ -7863,10 +10107,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G174" s="63" t="inlineStr"/>
-      <c r="H174" s="63" t="inlineStr"/>
-      <c r="I174" s="63" t="inlineStr"/>
-      <c r="J174" s="23" t="inlineStr"/>
+      <c r="G174" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H174" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I174" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J174" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K174" s="23" t="n"/>
       <c r="L174" s="64" t="inlineStr"/>
     </row>
@@ -7901,10 +10161,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G175" s="63" t="inlineStr"/>
-      <c r="H175" s="63" t="inlineStr"/>
-      <c r="I175" s="63" t="inlineStr"/>
-      <c r="J175" s="23" t="inlineStr"/>
+      <c r="G175" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H175" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I175" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J175" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K175" s="23" t="n"/>
       <c r="L175" s="64" t="inlineStr"/>
     </row>
@@ -7939,10 +10215,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G176" s="63" t="inlineStr"/>
-      <c r="H176" s="63" t="inlineStr"/>
-      <c r="I176" s="63" t="inlineStr"/>
-      <c r="J176" s="23" t="inlineStr"/>
+      <c r="G176" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H176" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I176" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J176" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K176" s="23" t="n"/>
       <c r="L176" s="64" t="inlineStr"/>
     </row>
@@ -7957,9 +10249,9 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C177" s="76" t="inlineStr">
-        <is>
-          <t>85%</t>
+      <c r="C177" s="77" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="D177" s="23" t="inlineStr">
@@ -7977,10 +10269,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G177" s="63" t="inlineStr"/>
-      <c r="H177" s="63" t="inlineStr"/>
-      <c r="I177" s="63" t="inlineStr"/>
-      <c r="J177" s="23" t="inlineStr"/>
+      <c r="G177" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H177" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I177" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J177" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K177" s="23" t="n"/>
       <c r="L177" s="64" t="inlineStr"/>
     </row>
@@ -7995,9 +10303,9 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C178" s="76" t="inlineStr">
-        <is>
-          <t>85%</t>
+      <c r="C178" s="77" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="D178" s="23" t="inlineStr">
@@ -8015,10 +10323,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G178" s="63" t="inlineStr"/>
-      <c r="H178" s="63" t="inlineStr"/>
-      <c r="I178" s="63" t="inlineStr"/>
-      <c r="J178" s="23" t="inlineStr"/>
+      <c r="G178" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H178" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I178" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J178" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K178" s="23" t="n"/>
       <c r="L178" s="64" t="inlineStr"/>
     </row>
@@ -8035,7 +10359,7 @@
       </c>
       <c r="C179" s="76" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="D179" s="23" t="inlineStr">
@@ -8053,10 +10377,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G179" s="63" t="inlineStr"/>
-      <c r="H179" s="63" t="inlineStr"/>
-      <c r="I179" s="63" t="inlineStr"/>
-      <c r="J179" s="23" t="inlineStr"/>
+      <c r="G179" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H179" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I179" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J179" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K179" s="23" t="n"/>
       <c r="L179" s="64" t="inlineStr"/>
     </row>
@@ -8073,7 +10413,7 @@
       </c>
       <c r="C180" s="76" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="D180" s="23" t="inlineStr">
@@ -8091,10 +10431,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G180" s="63" t="inlineStr"/>
-      <c r="H180" s="63" t="inlineStr"/>
-      <c r="I180" s="63" t="inlineStr"/>
-      <c r="J180" s="23" t="inlineStr"/>
+      <c r="G180" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H180" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I180" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J180" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K180" s="23" t="n"/>
       <c r="L180" s="64" t="inlineStr"/>
     </row>
@@ -8129,10 +10485,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G181" s="63" t="inlineStr"/>
-      <c r="H181" s="63" t="inlineStr"/>
-      <c r="I181" s="63" t="inlineStr"/>
-      <c r="J181" s="23" t="inlineStr"/>
+      <c r="G181" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H181" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I181" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J181" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K181" s="23" t="n"/>
       <c r="L181" s="64" t="inlineStr"/>
     </row>
@@ -8167,10 +10539,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G182" s="63" t="inlineStr"/>
-      <c r="H182" s="63" t="inlineStr"/>
-      <c r="I182" s="63" t="inlineStr"/>
-      <c r="J182" s="23" t="inlineStr"/>
+      <c r="G182" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H182" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I182" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J182" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K182" s="23" t="n"/>
       <c r="L182" s="64" t="inlineStr"/>
     </row>
@@ -8205,10 +10593,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G183" s="63" t="inlineStr"/>
-      <c r="H183" s="63" t="inlineStr"/>
-      <c r="I183" s="63" t="inlineStr"/>
-      <c r="J183" s="23" t="inlineStr"/>
+      <c r="G183" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H183" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I183" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J183" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K183" s="23" t="n"/>
       <c r="L183" s="64" t="inlineStr"/>
     </row>
@@ -8243,10 +10647,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G184" s="63" t="inlineStr"/>
-      <c r="H184" s="63" t="inlineStr"/>
-      <c r="I184" s="63" t="inlineStr"/>
-      <c r="J184" s="23" t="inlineStr"/>
+      <c r="G184" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H184" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I184" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J184" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K184" s="23" t="n"/>
       <c r="L184" s="64" t="inlineStr"/>
     </row>
@@ -8281,10 +10701,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G185" s="63" t="inlineStr"/>
-      <c r="H185" s="63" t="inlineStr"/>
-      <c r="I185" s="63" t="inlineStr"/>
-      <c r="J185" s="23" t="inlineStr"/>
+      <c r="G185" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H185" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I185" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J185" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K185" s="23" t="n"/>
       <c r="L185" s="64" t="inlineStr"/>
     </row>
@@ -8319,10 +10755,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G186" s="63" t="inlineStr"/>
-      <c r="H186" s="63" t="inlineStr"/>
-      <c r="I186" s="63" t="inlineStr"/>
-      <c r="J186" s="23" t="inlineStr"/>
+      <c r="G186" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H186" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I186" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J186" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K186" s="23" t="n"/>
       <c r="L186" s="64" t="inlineStr"/>
     </row>
@@ -8357,10 +10809,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G187" s="63" t="inlineStr"/>
-      <c r="H187" s="63" t="inlineStr"/>
-      <c r="I187" s="63" t="inlineStr"/>
-      <c r="J187" s="23" t="inlineStr"/>
+      <c r="G187" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H187" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I187" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J187" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K187" s="23" t="n"/>
       <c r="L187" s="64" t="inlineStr"/>
     </row>
@@ -8395,10 +10863,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G188" s="63" t="inlineStr"/>
-      <c r="H188" s="63" t="inlineStr"/>
-      <c r="I188" s="63" t="inlineStr"/>
-      <c r="J188" s="23" t="inlineStr"/>
+      <c r="G188" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H188" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I188" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J188" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K188" s="23" t="n"/>
       <c r="L188" s="64" t="inlineStr"/>
     </row>
@@ -8415,7 +10899,7 @@
       </c>
       <c r="C189" s="76" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="D189" s="23" t="inlineStr">
@@ -8433,10 +10917,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G189" s="63" t="inlineStr"/>
-      <c r="H189" s="63" t="inlineStr"/>
-      <c r="I189" s="63" t="inlineStr"/>
-      <c r="J189" s="23" t="inlineStr"/>
+      <c r="G189" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H189" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I189" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J189" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K189" s="23" t="n"/>
       <c r="L189" s="64" t="inlineStr"/>
     </row>
@@ -8453,7 +10953,7 @@
       </c>
       <c r="C190" s="76" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="D190" s="23" t="inlineStr">
@@ -8471,10 +10971,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G190" s="63" t="inlineStr"/>
-      <c r="H190" s="63" t="inlineStr"/>
-      <c r="I190" s="63" t="inlineStr"/>
-      <c r="J190" s="23" t="inlineStr"/>
+      <c r="G190" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H190" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I190" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J190" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K190" s="23" t="n"/>
       <c r="L190" s="64" t="inlineStr"/>
     </row>
@@ -8509,10 +11025,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G191" s="63" t="inlineStr"/>
-      <c r="H191" s="63" t="inlineStr"/>
-      <c r="I191" s="63" t="inlineStr"/>
-      <c r="J191" s="23" t="inlineStr"/>
+      <c r="G191" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H191" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I191" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J191" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K191" s="23" t="n"/>
       <c r="L191" s="64" t="inlineStr"/>
     </row>
@@ -8529,7 +11061,7 @@
       </c>
       <c r="C192" s="75" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="D192" s="23" t="inlineStr">
@@ -8547,10 +11079,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G192" s="63" t="inlineStr"/>
-      <c r="H192" s="63" t="inlineStr"/>
-      <c r="I192" s="63" t="inlineStr"/>
-      <c r="J192" s="23" t="inlineStr"/>
+      <c r="G192" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H192" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I192" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J192" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K192" s="23" t="n"/>
       <c r="L192" s="64" t="inlineStr"/>
     </row>
@@ -8585,10 +11133,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G193" s="63" t="inlineStr"/>
-      <c r="H193" s="63" t="inlineStr"/>
-      <c r="I193" s="63" t="inlineStr"/>
-      <c r="J193" s="23" t="inlineStr"/>
+      <c r="G193" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H193" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I193" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J193" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K193" s="23" t="n"/>
       <c r="L193" s="64" t="inlineStr"/>
     </row>
@@ -8605,7 +11169,7 @@
       </c>
       <c r="C194" s="75" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="D194" s="23" t="inlineStr">
@@ -8623,10 +11187,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G194" s="63" t="inlineStr"/>
-      <c r="H194" s="63" t="inlineStr"/>
-      <c r="I194" s="63" t="inlineStr"/>
-      <c r="J194" s="23" t="inlineStr"/>
+      <c r="G194" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H194" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I194" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J194" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K194" s="23" t="n"/>
       <c r="L194" s="64" t="inlineStr"/>
     </row>
@@ -8661,10 +11241,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G195" s="63" t="inlineStr"/>
-      <c r="H195" s="63" t="inlineStr"/>
-      <c r="I195" s="63" t="inlineStr"/>
-      <c r="J195" s="23" t="inlineStr"/>
+      <c r="G195" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H195" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I195" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J195" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K195" s="23" t="n"/>
       <c r="L195" s="64" t="inlineStr"/>
     </row>
@@ -8699,10 +11295,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G196" s="63" t="inlineStr"/>
-      <c r="H196" s="63" t="inlineStr"/>
-      <c r="I196" s="63" t="inlineStr"/>
-      <c r="J196" s="23" t="inlineStr"/>
+      <c r="G196" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H196" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I196" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J196" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K196" s="23" t="n"/>
       <c r="L196" s="64" t="inlineStr"/>
     </row>
@@ -8737,10 +11349,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G197" s="63" t="inlineStr"/>
-      <c r="H197" s="63" t="inlineStr"/>
-      <c r="I197" s="63" t="inlineStr"/>
-      <c r="J197" s="23" t="inlineStr"/>
+      <c r="G197" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H197" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I197" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J197" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K197" s="23" t="n"/>
       <c r="L197" s="64" t="inlineStr"/>
     </row>
@@ -8757,7 +11385,7 @@
       </c>
       <c r="C198" s="77" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D198" s="23" t="inlineStr">
@@ -8775,10 +11403,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G198" s="63" t="inlineStr"/>
-      <c r="H198" s="63" t="inlineStr"/>
-      <c r="I198" s="63" t="inlineStr"/>
-      <c r="J198" s="23" t="inlineStr"/>
+      <c r="G198" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H198" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I198" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J198" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K198" s="23" t="n"/>
       <c r="L198" s="64" t="inlineStr"/>
     </row>
@@ -8795,7 +11439,7 @@
       </c>
       <c r="C199" s="77" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D199" s="23" t="inlineStr">
@@ -8813,10 +11457,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G199" s="63" t="inlineStr"/>
-      <c r="H199" s="63" t="inlineStr"/>
-      <c r="I199" s="63" t="inlineStr"/>
-      <c r="J199" s="23" t="inlineStr"/>
+      <c r="G199" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H199" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I199" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J199" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K199" s="23" t="n"/>
       <c r="L199" s="64" t="inlineStr"/>
     </row>
@@ -8831,9 +11491,9 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C200" s="76" t="inlineStr">
-        <is>
-          <t>83%</t>
+      <c r="C200" s="77" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="D200" s="23" t="inlineStr">
@@ -8851,10 +11511,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G200" s="63" t="inlineStr"/>
-      <c r="H200" s="63" t="inlineStr"/>
-      <c r="I200" s="63" t="inlineStr"/>
-      <c r="J200" s="23" t="inlineStr"/>
+      <c r="G200" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H200" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I200" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J200" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K200" s="23" t="n"/>
       <c r="L200" s="64" t="inlineStr"/>
     </row>
@@ -8869,9 +11545,9 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C201" s="76" t="inlineStr">
-        <is>
-          <t>83%</t>
+      <c r="C201" s="77" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="D201" s="23" t="inlineStr">
@@ -8889,10 +11565,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G201" s="63" t="inlineStr"/>
-      <c r="H201" s="63" t="inlineStr"/>
-      <c r="I201" s="63" t="inlineStr"/>
-      <c r="J201" s="23" t="inlineStr"/>
+      <c r="G201" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H201" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I201" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J201" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K201" s="23" t="n"/>
       <c r="L201" s="64" t="inlineStr"/>
     </row>
@@ -8909,7 +11601,7 @@
       </c>
       <c r="C202" s="76" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="D202" s="23" t="inlineStr">
@@ -8927,10 +11619,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G202" s="63" t="inlineStr"/>
-      <c r="H202" s="63" t="inlineStr"/>
-      <c r="I202" s="63" t="inlineStr"/>
-      <c r="J202" s="23" t="inlineStr"/>
+      <c r="G202" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H202" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I202" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J202" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K202" s="23" t="n"/>
       <c r="L202" s="64" t="inlineStr"/>
     </row>
@@ -8947,7 +11655,7 @@
       </c>
       <c r="C203" s="76" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="D203" s="23" t="inlineStr">
@@ -8965,10 +11673,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G203" s="63" t="inlineStr"/>
-      <c r="H203" s="63" t="inlineStr"/>
-      <c r="I203" s="63" t="inlineStr"/>
-      <c r="J203" s="23" t="inlineStr"/>
+      <c r="G203" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H203" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I203" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J203" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K203" s="23" t="n"/>
       <c r="L203" s="64" t="inlineStr"/>
     </row>
@@ -8985,7 +11709,7 @@
       </c>
       <c r="C204" s="75" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="D204" s="23" t="inlineStr">
@@ -9003,10 +11727,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G204" s="63" t="inlineStr"/>
-      <c r="H204" s="63" t="inlineStr"/>
-      <c r="I204" s="63" t="inlineStr"/>
-      <c r="J204" s="23" t="inlineStr"/>
+      <c r="G204" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H204" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I204" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J204" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K204" s="23" t="n"/>
       <c r="L204" s="64" t="inlineStr"/>
     </row>
@@ -9041,10 +11781,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G205" s="63" t="inlineStr"/>
-      <c r="H205" s="63" t="inlineStr"/>
-      <c r="I205" s="63" t="inlineStr"/>
-      <c r="J205" s="23" t="inlineStr"/>
+      <c r="G205" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H205" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I205" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J205" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K205" s="23" t="n"/>
       <c r="L205" s="64" t="inlineStr"/>
     </row>
@@ -9079,10 +11835,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G206" s="63" t="inlineStr"/>
-      <c r="H206" s="63" t="inlineStr"/>
-      <c r="I206" s="63" t="inlineStr"/>
-      <c r="J206" s="23" t="inlineStr"/>
+      <c r="G206" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H206" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I206" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J206" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K206" s="23" t="n"/>
       <c r="L206" s="64" t="inlineStr"/>
     </row>
@@ -9117,10 +11889,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G207" s="63" t="inlineStr"/>
-      <c r="H207" s="63" t="inlineStr"/>
-      <c r="I207" s="63" t="inlineStr"/>
-      <c r="J207" s="23" t="inlineStr"/>
+      <c r="G207" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H207" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I207" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J207" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K207" s="23" t="n"/>
       <c r="L207" s="64" t="inlineStr"/>
     </row>
@@ -9155,10 +11943,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G208" s="63" t="inlineStr"/>
-      <c r="H208" s="63" t="inlineStr"/>
-      <c r="I208" s="63" t="inlineStr"/>
-      <c r="J208" s="23" t="inlineStr"/>
+      <c r="G208" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H208" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I208" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J208" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K208" s="23" t="n"/>
       <c r="L208" s="64" t="inlineStr"/>
     </row>
@@ -9193,10 +11997,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G209" s="63" t="inlineStr"/>
-      <c r="H209" s="63" t="inlineStr"/>
-      <c r="I209" s="63" t="inlineStr"/>
-      <c r="J209" s="23" t="inlineStr"/>
+      <c r="G209" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H209" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I209" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J209" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K209" s="23" t="n"/>
       <c r="L209" s="64" t="inlineStr"/>
     </row>
@@ -9231,10 +12051,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G210" s="63" t="inlineStr"/>
-      <c r="H210" s="63" t="inlineStr"/>
-      <c r="I210" s="63" t="inlineStr"/>
-      <c r="J210" s="23" t="inlineStr"/>
+      <c r="G210" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H210" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I210" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J210" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K210" s="23" t="n"/>
       <c r="L210" s="64" t="inlineStr"/>
     </row>
@@ -9269,10 +12105,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G211" s="63" t="inlineStr"/>
-      <c r="H211" s="63" t="inlineStr"/>
-      <c r="I211" s="63" t="inlineStr"/>
-      <c r="J211" s="23" t="inlineStr"/>
+      <c r="G211" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H211" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I211" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J211" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K211" s="23" t="n"/>
       <c r="L211" s="64" t="inlineStr"/>
     </row>
@@ -9307,10 +12159,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G212" s="63" t="inlineStr"/>
-      <c r="H212" s="63" t="inlineStr"/>
-      <c r="I212" s="63" t="inlineStr"/>
-      <c r="J212" s="23" t="inlineStr"/>
+      <c r="G212" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H212" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I212" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J212" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K212" s="23" t="n"/>
       <c r="L212" s="64" t="inlineStr"/>
     </row>
@@ -9373,10 +12241,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G214" s="63" t="inlineStr"/>
-      <c r="H214" s="63" t="inlineStr"/>
-      <c r="I214" s="63" t="inlineStr"/>
-      <c r="J214" s="23" t="inlineStr"/>
+      <c r="G214" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H214" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I214" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J214" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K214" s="23" t="n"/>
       <c r="L214" s="64" t="inlineStr"/>
     </row>
@@ -9411,10 +12295,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G215" s="63" t="inlineStr"/>
-      <c r="H215" s="63" t="inlineStr"/>
-      <c r="I215" s="63" t="inlineStr"/>
-      <c r="J215" s="23" t="inlineStr"/>
+      <c r="G215" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H215" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I215" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J215" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K215" s="23" t="n"/>
       <c r="L215" s="64" t="inlineStr"/>
     </row>
@@ -9449,10 +12349,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G216" s="63" t="inlineStr"/>
-      <c r="H216" s="63" t="inlineStr"/>
-      <c r="I216" s="63" t="inlineStr"/>
-      <c r="J216" s="23" t="inlineStr"/>
+      <c r="G216" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H216" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I216" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J216" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K216" s="23" t="n"/>
       <c r="L216" s="64" t="inlineStr"/>
     </row>
@@ -9487,10 +12403,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G217" s="63" t="inlineStr"/>
-      <c r="H217" s="63" t="inlineStr"/>
-      <c r="I217" s="63" t="inlineStr"/>
-      <c r="J217" s="23" t="inlineStr"/>
+      <c r="G217" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H217" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I217" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J217" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K217" s="23" t="n"/>
       <c r="L217" s="64" t="inlineStr"/>
     </row>
@@ -9525,10 +12457,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G218" s="63" t="inlineStr"/>
-      <c r="H218" s="63" t="inlineStr"/>
-      <c r="I218" s="63" t="inlineStr"/>
-      <c r="J218" s="23" t="inlineStr"/>
+      <c r="G218" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H218" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I218" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J218" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K218" s="23" t="n"/>
       <c r="L218" s="64" t="inlineStr"/>
     </row>
@@ -9563,10 +12511,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G219" s="63" t="inlineStr"/>
-      <c r="H219" s="63" t="inlineStr"/>
-      <c r="I219" s="63" t="inlineStr"/>
-      <c r="J219" s="23" t="inlineStr"/>
+      <c r="G219" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H219" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I219" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J219" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K219" s="23" t="n"/>
       <c r="L219" s="64" t="inlineStr"/>
     </row>
@@ -9601,10 +12565,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G220" s="63" t="inlineStr"/>
-      <c r="H220" s="63" t="inlineStr"/>
-      <c r="I220" s="63" t="inlineStr"/>
-      <c r="J220" s="23" t="inlineStr"/>
+      <c r="G220" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H220" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I220" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J220" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K220" s="23" t="n"/>
       <c r="L220" s="64" t="inlineStr"/>
     </row>
@@ -9639,10 +12619,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G221" s="63" t="inlineStr"/>
-      <c r="H221" s="63" t="inlineStr"/>
-      <c r="I221" s="63" t="inlineStr"/>
-      <c r="J221" s="23" t="inlineStr"/>
+      <c r="G221" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H221" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I221" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J221" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K221" s="23" t="n"/>
       <c r="L221" s="64" t="inlineStr"/>
     </row>
@@ -9677,10 +12673,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G222" s="63" t="inlineStr"/>
-      <c r="H222" s="63" t="inlineStr"/>
-      <c r="I222" s="63" t="inlineStr"/>
-      <c r="J222" s="23" t="inlineStr"/>
+      <c r="G222" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H222" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I222" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J222" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K222" s="23" t="n"/>
       <c r="L222" s="64" t="inlineStr"/>
     </row>
@@ -9715,10 +12727,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G223" s="63" t="inlineStr"/>
-      <c r="H223" s="63" t="inlineStr"/>
-      <c r="I223" s="63" t="inlineStr"/>
-      <c r="J223" s="23" t="inlineStr"/>
+      <c r="G223" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H223" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I223" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J223" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K223" s="23" t="n"/>
       <c r="L223" s="64" t="inlineStr"/>
     </row>
@@ -9753,10 +12781,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G224" s="63" t="inlineStr"/>
-      <c r="H224" s="63" t="inlineStr"/>
-      <c r="I224" s="63" t="inlineStr"/>
-      <c r="J224" s="23" t="inlineStr"/>
+      <c r="G224" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H224" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I224" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J224" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K224" s="23" t="n"/>
       <c r="L224" s="64" t="inlineStr"/>
     </row>
@@ -9791,10 +12835,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G225" s="63" t="inlineStr"/>
-      <c r="H225" s="63" t="inlineStr"/>
-      <c r="I225" s="63" t="inlineStr"/>
-      <c r="J225" s="23" t="inlineStr"/>
+      <c r="G225" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H225" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I225" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J225" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K225" s="23" t="n"/>
       <c r="L225" s="64" t="inlineStr"/>
     </row>
@@ -9829,10 +12889,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G226" s="63" t="inlineStr"/>
-      <c r="H226" s="63" t="inlineStr"/>
-      <c r="I226" s="63" t="inlineStr"/>
-      <c r="J226" s="23" t="inlineStr"/>
+      <c r="G226" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H226" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I226" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J226" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K226" s="23" t="n"/>
       <c r="L226" s="64" t="inlineStr"/>
     </row>
@@ -9923,10 +12999,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G229" s="63" t="inlineStr"/>
-      <c r="H229" s="63" t="inlineStr"/>
-      <c r="I229" s="63" t="inlineStr"/>
-      <c r="J229" s="23" t="inlineStr"/>
+      <c r="G229" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H229" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I229" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J229" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K229" s="23" t="n"/>
       <c r="L229" s="64" t="inlineStr"/>
     </row>
@@ -9961,10 +13053,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G230" s="63" t="inlineStr"/>
-      <c r="H230" s="63" t="inlineStr"/>
-      <c r="I230" s="63" t="inlineStr"/>
-      <c r="J230" s="23" t="inlineStr"/>
+      <c r="G230" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H230" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I230" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J230" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K230" s="23" t="n"/>
       <c r="L230" s="64" t="inlineStr"/>
     </row>
@@ -9999,10 +13107,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G231" s="63" t="inlineStr"/>
-      <c r="H231" s="63" t="inlineStr"/>
-      <c r="I231" s="63" t="inlineStr"/>
-      <c r="J231" s="23" t="inlineStr"/>
+      <c r="G231" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H231" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I231" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J231" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K231" s="23" t="n"/>
       <c r="L231" s="64" t="inlineStr"/>
     </row>
@@ -10037,10 +13161,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G232" s="63" t="inlineStr"/>
-      <c r="H232" s="63" t="inlineStr"/>
-      <c r="I232" s="63" t="inlineStr"/>
-      <c r="J232" s="23" t="inlineStr"/>
+      <c r="G232" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H232" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I232" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J232" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K232" s="23" t="n"/>
       <c r="L232" s="64" t="inlineStr"/>
     </row>
@@ -10075,10 +13215,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G233" s="63" t="inlineStr"/>
-      <c r="H233" s="63" t="inlineStr"/>
-      <c r="I233" s="63" t="inlineStr"/>
-      <c r="J233" s="23" t="inlineStr"/>
+      <c r="G233" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H233" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I233" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J233" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K233" s="23" t="n"/>
       <c r="L233" s="64" t="inlineStr"/>
     </row>
@@ -10113,10 +13269,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G234" s="63" t="inlineStr"/>
-      <c r="H234" s="63" t="inlineStr"/>
-      <c r="I234" s="63" t="inlineStr"/>
-      <c r="J234" s="23" t="inlineStr"/>
+      <c r="G234" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H234" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I234" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J234" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K234" s="23" t="n"/>
       <c r="L234" s="64" t="inlineStr"/>
     </row>
@@ -10151,10 +13323,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G235" s="63" t="inlineStr"/>
-      <c r="H235" s="63" t="inlineStr"/>
-      <c r="I235" s="63" t="inlineStr"/>
-      <c r="J235" s="23" t="inlineStr"/>
+      <c r="G235" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H235" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I235" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J235" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K235" s="23" t="n"/>
       <c r="L235" s="64" t="inlineStr"/>
     </row>
@@ -10189,10 +13377,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G236" s="63" t="inlineStr"/>
-      <c r="H236" s="63" t="inlineStr"/>
-      <c r="I236" s="63" t="inlineStr"/>
-      <c r="J236" s="23" t="inlineStr"/>
+      <c r="G236" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H236" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I236" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J236" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K236" s="23" t="n"/>
       <c r="L236" s="64" t="inlineStr"/>
     </row>
@@ -10255,10 +13459,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G238" s="63" t="inlineStr"/>
-      <c r="H238" s="63" t="inlineStr"/>
-      <c r="I238" s="63" t="inlineStr"/>
-      <c r="J238" s="23" t="inlineStr"/>
+      <c r="G238" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H238" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I238" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J238" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K238" s="23" t="n"/>
       <c r="L238" s="64" t="inlineStr"/>
     </row>
@@ -10293,10 +13513,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G239" s="63" t="inlineStr"/>
-      <c r="H239" s="63" t="inlineStr"/>
-      <c r="I239" s="63" t="inlineStr"/>
-      <c r="J239" s="23" t="inlineStr"/>
+      <c r="G239" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H239" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I239" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J239" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K239" s="23" t="n"/>
       <c r="L239" s="64" t="inlineStr"/>
     </row>
@@ -10331,10 +13567,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G240" s="63" t="inlineStr"/>
-      <c r="H240" s="63" t="inlineStr"/>
-      <c r="I240" s="63" t="inlineStr"/>
-      <c r="J240" s="23" t="inlineStr"/>
+      <c r="G240" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H240" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I240" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J240" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K240" s="23" t="n"/>
       <c r="L240" s="64" t="inlineStr"/>
     </row>
@@ -10369,10 +13621,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G241" s="63" t="inlineStr"/>
-      <c r="H241" s="63" t="inlineStr"/>
-      <c r="I241" s="63" t="inlineStr"/>
-      <c r="J241" s="23" t="inlineStr"/>
+      <c r="G241" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H241" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I241" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J241" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K241" s="23" t="n"/>
       <c r="L241" s="64" t="inlineStr"/>
     </row>
@@ -10407,10 +13675,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G242" s="63" t="inlineStr"/>
-      <c r="H242" s="63" t="inlineStr"/>
-      <c r="I242" s="63" t="inlineStr"/>
-      <c r="J242" s="23" t="inlineStr"/>
+      <c r="G242" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H242" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I242" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J242" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K242" s="23" t="n"/>
       <c r="L242" s="64" t="inlineStr"/>
     </row>
@@ -10473,10 +13757,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G244" s="63" t="inlineStr"/>
-      <c r="H244" s="63" t="inlineStr"/>
-      <c r="I244" s="63" t="inlineStr"/>
-      <c r="J244" s="23" t="inlineStr"/>
+      <c r="G244" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H244" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I244" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J244" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K244" s="23" t="n"/>
       <c r="L244" s="64" t="inlineStr"/>
     </row>
@@ -10511,10 +13811,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G245" s="63" t="inlineStr"/>
-      <c r="H245" s="63" t="inlineStr"/>
-      <c r="I245" s="63" t="inlineStr"/>
-      <c r="J245" s="23" t="inlineStr"/>
+      <c r="G245" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H245" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I245" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J245" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K245" s="23" t="n"/>
       <c r="L245" s="64" t="inlineStr"/>
     </row>
@@ -10549,10 +13865,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G246" s="63" t="inlineStr"/>
-      <c r="H246" s="63" t="inlineStr"/>
-      <c r="I246" s="63" t="inlineStr"/>
-      <c r="J246" s="23" t="inlineStr"/>
+      <c r="G246" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H246" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I246" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J246" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K246" s="23" t="n"/>
       <c r="L246" s="64" t="inlineStr"/>
     </row>
@@ -10587,10 +13919,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G247" s="63" t="inlineStr"/>
-      <c r="H247" s="63" t="inlineStr"/>
-      <c r="I247" s="63" t="inlineStr"/>
-      <c r="J247" s="23" t="inlineStr"/>
+      <c r="G247" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H247" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I247" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J247" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K247" s="23" t="n"/>
       <c r="L247" s="64" t="inlineStr"/>
     </row>
@@ -10625,10 +13973,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G248" s="63" t="inlineStr"/>
-      <c r="H248" s="63" t="inlineStr"/>
-      <c r="I248" s="63" t="inlineStr"/>
-      <c r="J248" s="23" t="inlineStr"/>
+      <c r="G248" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H248" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I248" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J248" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K248" s="23" t="n"/>
       <c r="L248" s="64" t="inlineStr"/>
     </row>
@@ -10663,10 +14027,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G249" s="63" t="inlineStr"/>
-      <c r="H249" s="63" t="inlineStr"/>
-      <c r="I249" s="63" t="inlineStr"/>
-      <c r="J249" s="23" t="inlineStr"/>
+      <c r="G249" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H249" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I249" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J249" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K249" s="23" t="n"/>
       <c r="L249" s="64" t="inlineStr"/>
     </row>
@@ -10701,10 +14081,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G250" s="63" t="inlineStr"/>
-      <c r="H250" s="63" t="inlineStr"/>
-      <c r="I250" s="63" t="inlineStr"/>
-      <c r="J250" s="23" t="inlineStr"/>
+      <c r="G250" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H250" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I250" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J250" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K250" s="23" t="n"/>
       <c r="L250" s="64" t="inlineStr"/>
     </row>
@@ -10739,10 +14135,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G251" s="63" t="inlineStr"/>
-      <c r="H251" s="63" t="inlineStr"/>
-      <c r="I251" s="63" t="inlineStr"/>
-      <c r="J251" s="23" t="inlineStr"/>
+      <c r="G251" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H251" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I251" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J251" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K251" s="23" t="n"/>
       <c r="L251" s="64" t="inlineStr"/>
     </row>
@@ -10777,10 +14189,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G252" s="63" t="inlineStr"/>
-      <c r="H252" s="63" t="inlineStr"/>
-      <c r="I252" s="63" t="inlineStr"/>
-      <c r="J252" s="23" t="inlineStr"/>
+      <c r="G252" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H252" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I252" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J252" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K252" s="23" t="n"/>
       <c r="L252" s="64" t="inlineStr"/>
     </row>
@@ -10797,7 +14225,7 @@
       </c>
       <c r="C253" s="77" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D253" s="23" t="inlineStr">
@@ -10815,10 +14243,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G253" s="63" t="inlineStr"/>
-      <c r="H253" s="63" t="inlineStr"/>
-      <c r="I253" s="63" t="inlineStr"/>
-      <c r="J253" s="23" t="inlineStr"/>
+      <c r="G253" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H253" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I253" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J253" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K253" s="23" t="n"/>
       <c r="L253" s="64" t="inlineStr"/>
     </row>
@@ -10853,10 +14297,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G254" s="63" t="inlineStr"/>
-      <c r="H254" s="63" t="inlineStr"/>
-      <c r="I254" s="63" t="inlineStr"/>
-      <c r="J254" s="23" t="inlineStr"/>
+      <c r="G254" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H254" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I254" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J254" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K254" s="23" t="n"/>
       <c r="L254" s="64" t="inlineStr"/>
     </row>
@@ -10891,10 +14351,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G255" s="63" t="inlineStr"/>
-      <c r="H255" s="63" t="inlineStr"/>
-      <c r="I255" s="63" t="inlineStr"/>
-      <c r="J255" s="23" t="inlineStr"/>
+      <c r="G255" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H255" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I255" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J255" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K255" s="23" t="n"/>
       <c r="L255" s="64" t="inlineStr"/>
     </row>
@@ -10929,10 +14405,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G256" s="63" t="inlineStr"/>
-      <c r="H256" s="63" t="inlineStr"/>
-      <c r="I256" s="63" t="inlineStr"/>
-      <c r="J256" s="23" t="inlineStr"/>
+      <c r="G256" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H256" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I256" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J256" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K256" s="23" t="n"/>
       <c r="L256" s="64" t="inlineStr"/>
     </row>
@@ -10949,7 +14441,7 @@
       </c>
       <c r="C257" s="75" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="D257" s="23" t="inlineStr">
@@ -10967,10 +14459,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G257" s="63" t="inlineStr"/>
-      <c r="H257" s="63" t="inlineStr"/>
-      <c r="I257" s="63" t="inlineStr"/>
-      <c r="J257" s="23" t="inlineStr"/>
+      <c r="G257" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H257" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I257" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J257" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K257" s="23" t="n"/>
       <c r="L257" s="64" t="inlineStr"/>
     </row>
@@ -11005,10 +14513,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G258" s="63" t="inlineStr"/>
-      <c r="H258" s="63" t="inlineStr"/>
-      <c r="I258" s="63" t="inlineStr"/>
-      <c r="J258" s="23" t="inlineStr"/>
+      <c r="G258" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H258" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I258" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J258" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K258" s="23" t="n"/>
       <c r="L258" s="64" t="inlineStr"/>
     </row>
@@ -11025,7 +14549,7 @@
       </c>
       <c r="C259" s="75" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="D259" s="23" t="inlineStr">
@@ -11043,10 +14567,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G259" s="63" t="inlineStr"/>
-      <c r="H259" s="63" t="inlineStr"/>
-      <c r="I259" s="63" t="inlineStr"/>
-      <c r="J259" s="23" t="inlineStr"/>
+      <c r="G259" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H259" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I259" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J259" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K259" s="23" t="n"/>
       <c r="L259" s="64" t="inlineStr"/>
     </row>
@@ -11081,10 +14621,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G260" s="63" t="inlineStr"/>
-      <c r="H260" s="63" t="inlineStr"/>
-      <c r="I260" s="63" t="inlineStr"/>
-      <c r="J260" s="23" t="inlineStr"/>
+      <c r="G260" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H260" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I260" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J260" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K260" s="23" t="n"/>
       <c r="L260" s="64" t="inlineStr"/>
     </row>
@@ -11119,10 +14675,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G261" s="63" t="inlineStr"/>
-      <c r="H261" s="63" t="inlineStr"/>
-      <c r="I261" s="63" t="inlineStr"/>
-      <c r="J261" s="23" t="inlineStr"/>
+      <c r="G261" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H261" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I261" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J261" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K261" s="23" t="n"/>
       <c r="L261" s="64" t="inlineStr"/>
     </row>
@@ -11157,10 +14729,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G262" s="63" t="inlineStr"/>
-      <c r="H262" s="63" t="inlineStr"/>
-      <c r="I262" s="63" t="inlineStr"/>
-      <c r="J262" s="23" t="inlineStr"/>
+      <c r="G262" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H262" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I262" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J262" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K262" s="23" t="n"/>
       <c r="L262" s="64" t="inlineStr"/>
     </row>
@@ -11195,10 +14783,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G263" s="63" t="inlineStr"/>
-      <c r="H263" s="63" t="inlineStr"/>
-      <c r="I263" s="63" t="inlineStr"/>
-      <c r="J263" s="23" t="inlineStr"/>
+      <c r="G263" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H263" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I263" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J263" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K263" s="23" t="n"/>
       <c r="L263" s="64" t="inlineStr"/>
     </row>
@@ -11233,10 +14837,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G264" s="63" t="inlineStr"/>
-      <c r="H264" s="63" t="inlineStr"/>
-      <c r="I264" s="63" t="inlineStr"/>
-      <c r="J264" s="23" t="inlineStr"/>
+      <c r="G264" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H264" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I264" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J264" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K264" s="23" t="n"/>
       <c r="L264" s="64" t="inlineStr"/>
     </row>
@@ -11271,10 +14891,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G265" s="63" t="inlineStr"/>
-      <c r="H265" s="63" t="inlineStr"/>
-      <c r="I265" s="63" t="inlineStr"/>
-      <c r="J265" s="23" t="inlineStr"/>
+      <c r="G265" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H265" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I265" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J265" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K265" s="23" t="n"/>
       <c r="L265" s="64" t="inlineStr"/>
     </row>
@@ -11309,10 +14945,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G266" s="63" t="inlineStr"/>
-      <c r="H266" s="63" t="inlineStr"/>
-      <c r="I266" s="63" t="inlineStr"/>
-      <c r="J266" s="23" t="inlineStr"/>
+      <c r="G266" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H266" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I266" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J266" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K266" s="23" t="n"/>
       <c r="L266" s="64" t="inlineStr"/>
     </row>
@@ -11347,10 +14999,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G267" s="63" t="inlineStr"/>
-      <c r="H267" s="63" t="inlineStr"/>
-      <c r="I267" s="63" t="inlineStr"/>
-      <c r="J267" s="23" t="inlineStr"/>
+      <c r="G267" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H267" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I267" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J267" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K267" s="23" t="n"/>
       <c r="L267" s="64" t="inlineStr"/>
     </row>
@@ -11385,10 +15053,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G268" s="63" t="inlineStr"/>
-      <c r="H268" s="63" t="inlineStr"/>
-      <c r="I268" s="63" t="inlineStr"/>
-      <c r="J268" s="23" t="inlineStr"/>
+      <c r="G268" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H268" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I268" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J268" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K268" s="23" t="n"/>
       <c r="L268" s="64" t="inlineStr"/>
     </row>
@@ -11423,10 +15107,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G269" s="63" t="inlineStr"/>
-      <c r="H269" s="63" t="inlineStr"/>
-      <c r="I269" s="63" t="inlineStr"/>
-      <c r="J269" s="23" t="inlineStr"/>
+      <c r="G269" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H269" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I269" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J269" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K269" s="23" t="n"/>
       <c r="L269" s="64" t="inlineStr"/>
     </row>
@@ -11461,10 +15161,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G270" s="63" t="inlineStr"/>
-      <c r="H270" s="63" t="inlineStr"/>
-      <c r="I270" s="63" t="inlineStr"/>
-      <c r="J270" s="23" t="inlineStr"/>
+      <c r="G270" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H270" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I270" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J270" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K270" s="23" t="n"/>
       <c r="L270" s="64" t="inlineStr"/>
     </row>
@@ -11499,10 +15215,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G271" s="63" t="inlineStr"/>
-      <c r="H271" s="63" t="inlineStr"/>
-      <c r="I271" s="63" t="inlineStr"/>
-      <c r="J271" s="23" t="inlineStr"/>
+      <c r="G271" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H271" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I271" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J271" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K271" s="23" t="n"/>
       <c r="L271" s="64" t="inlineStr"/>
     </row>
@@ -11537,10 +15269,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G272" s="63" t="inlineStr"/>
-      <c r="H272" s="63" t="inlineStr"/>
-      <c r="I272" s="63" t="inlineStr"/>
-      <c r="J272" s="23" t="inlineStr"/>
+      <c r="G272" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H272" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I272" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J272" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K272" s="23" t="n"/>
       <c r="L272" s="64" t="inlineStr"/>
     </row>
@@ -11575,10 +15323,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G273" s="63" t="inlineStr"/>
-      <c r="H273" s="63" t="inlineStr"/>
-      <c r="I273" s="63" t="inlineStr"/>
-      <c r="J273" s="23" t="inlineStr"/>
+      <c r="G273" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H273" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I273" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J273" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K273" s="23" t="n"/>
       <c r="L273" s="64" t="inlineStr"/>
     </row>
@@ -11613,10 +15377,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G274" s="63" t="inlineStr"/>
-      <c r="H274" s="63" t="inlineStr"/>
-      <c r="I274" s="63" t="inlineStr"/>
-      <c r="J274" s="23" t="inlineStr"/>
+      <c r="G274" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H274" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I274" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J274" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K274" s="23" t="n"/>
       <c r="L274" s="64" t="inlineStr"/>
     </row>
@@ -11651,10 +15431,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G275" s="63" t="inlineStr"/>
-      <c r="H275" s="63" t="inlineStr"/>
-      <c r="I275" s="63" t="inlineStr"/>
-      <c r="J275" s="23" t="inlineStr"/>
+      <c r="G275" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H275" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I275" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J275" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K275" s="23" t="n"/>
       <c r="L275" s="64" t="inlineStr"/>
     </row>
@@ -11689,10 +15485,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G276" s="63" t="inlineStr"/>
-      <c r="H276" s="63" t="inlineStr"/>
-      <c r="I276" s="63" t="inlineStr"/>
-      <c r="J276" s="23" t="inlineStr"/>
+      <c r="G276" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H276" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I276" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J276" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K276" s="23" t="n"/>
       <c r="L276" s="64" t="inlineStr"/>
     </row>
@@ -11727,10 +15539,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G277" s="63" t="inlineStr"/>
-      <c r="H277" s="63" t="inlineStr"/>
-      <c r="I277" s="63" t="inlineStr"/>
-      <c r="J277" s="23" t="inlineStr"/>
+      <c r="G277" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H277" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I277" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J277" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K277" s="23" t="n"/>
       <c r="L277" s="64" t="inlineStr"/>
     </row>
@@ -11765,10 +15593,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G278" s="63" t="inlineStr"/>
-      <c r="H278" s="63" t="inlineStr"/>
-      <c r="I278" s="63" t="inlineStr"/>
-      <c r="J278" s="23" t="inlineStr"/>
+      <c r="G278" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H278" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I278" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J278" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K278" s="23" t="n"/>
       <c r="L278" s="64" t="inlineStr"/>
     </row>
@@ -11803,10 +15647,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G279" s="63" t="inlineStr"/>
-      <c r="H279" s="63" t="inlineStr"/>
-      <c r="I279" s="63" t="inlineStr"/>
-      <c r="J279" s="23" t="inlineStr"/>
+      <c r="G279" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H279" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I279" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J279" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K279" s="23" t="n"/>
       <c r="L279" s="64" t="inlineStr"/>
     </row>
@@ -11841,10 +15701,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G280" s="63" t="inlineStr"/>
-      <c r="H280" s="63" t="inlineStr"/>
-      <c r="I280" s="63" t="inlineStr"/>
-      <c r="J280" s="23" t="inlineStr"/>
+      <c r="G280" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H280" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I280" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J280" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K280" s="23" t="n"/>
       <c r="L280" s="64" t="inlineStr"/>
     </row>
@@ -11879,10 +15755,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G281" s="63" t="inlineStr"/>
-      <c r="H281" s="63" t="inlineStr"/>
-      <c r="I281" s="63" t="inlineStr"/>
-      <c r="J281" s="23" t="inlineStr"/>
+      <c r="G281" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H281" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I281" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J281" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K281" s="23" t="n"/>
       <c r="L281" s="64" t="inlineStr"/>
     </row>
@@ -11917,10 +15809,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G282" s="63" t="inlineStr"/>
-      <c r="H282" s="63" t="inlineStr"/>
-      <c r="I282" s="63" t="inlineStr"/>
-      <c r="J282" s="23" t="inlineStr"/>
+      <c r="G282" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H282" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I282" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J282" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K282" s="23" t="n"/>
       <c r="L282" s="64" t="inlineStr"/>
     </row>
@@ -11955,10 +15863,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G283" s="63" t="inlineStr"/>
-      <c r="H283" s="63" t="inlineStr"/>
-      <c r="I283" s="63" t="inlineStr"/>
-      <c r="J283" s="23" t="inlineStr"/>
+      <c r="G283" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H283" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I283" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J283" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K283" s="23" t="n"/>
       <c r="L283" s="64" t="inlineStr"/>
     </row>
@@ -11993,10 +15917,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G284" s="63" t="inlineStr"/>
-      <c r="H284" s="63" t="inlineStr"/>
-      <c r="I284" s="63" t="inlineStr"/>
-      <c r="J284" s="23" t="inlineStr"/>
+      <c r="G284" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H284" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I284" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J284" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K284" s="23" t="n"/>
       <c r="L284" s="64" t="inlineStr"/>
     </row>
@@ -12031,10 +15971,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G285" s="63" t="inlineStr"/>
-      <c r="H285" s="63" t="inlineStr"/>
-      <c r="I285" s="63" t="inlineStr"/>
-      <c r="J285" s="23" t="inlineStr"/>
+      <c r="G285" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H285" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I285" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J285" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K285" s="23" t="n"/>
       <c r="L285" s="64" t="inlineStr"/>
     </row>
@@ -12069,10 +16025,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G286" s="63" t="inlineStr"/>
-      <c r="H286" s="63" t="inlineStr"/>
-      <c r="I286" s="63" t="inlineStr"/>
-      <c r="J286" s="23" t="inlineStr"/>
+      <c r="G286" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H286" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I286" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J286" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K286" s="23" t="n"/>
       <c r="L286" s="64" t="inlineStr"/>
     </row>
@@ -12107,10 +16079,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G287" s="63" t="inlineStr"/>
-      <c r="H287" s="63" t="inlineStr"/>
-      <c r="I287" s="63" t="inlineStr"/>
-      <c r="J287" s="23" t="inlineStr"/>
+      <c r="G287" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H287" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I287" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J287" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K287" s="23" t="n"/>
       <c r="L287" s="64" t="inlineStr"/>
     </row>
@@ -12145,10 +16133,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G288" s="63" t="inlineStr"/>
-      <c r="H288" s="63" t="inlineStr"/>
-      <c r="I288" s="63" t="inlineStr"/>
-      <c r="J288" s="23" t="inlineStr"/>
+      <c r="G288" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H288" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I288" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J288" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K288" s="23" t="n"/>
       <c r="L288" s="64" t="inlineStr"/>
     </row>
@@ -12183,10 +16187,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G289" s="63" t="inlineStr"/>
-      <c r="H289" s="63" t="inlineStr"/>
-      <c r="I289" s="63" t="inlineStr"/>
-      <c r="J289" s="23" t="inlineStr"/>
+      <c r="G289" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H289" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I289" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J289" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K289" s="23" t="n"/>
       <c r="L289" s="64" t="inlineStr"/>
     </row>
@@ -12221,10 +16241,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G290" s="63" t="inlineStr"/>
-      <c r="H290" s="63" t="inlineStr"/>
-      <c r="I290" s="63" t="inlineStr"/>
-      <c r="J290" s="23" t="inlineStr"/>
+      <c r="G290" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H290" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I290" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J290" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K290" s="23" t="n"/>
       <c r="L290" s="64" t="inlineStr"/>
     </row>
@@ -12259,10 +16295,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G291" s="63" t="inlineStr"/>
-      <c r="H291" s="63" t="inlineStr"/>
-      <c r="I291" s="63" t="inlineStr"/>
-      <c r="J291" s="23" t="inlineStr"/>
+      <c r="G291" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H291" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I291" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J291" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K291" s="23" t="n"/>
       <c r="L291" s="64" t="inlineStr"/>
     </row>
@@ -12297,10 +16349,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G292" s="63" t="inlineStr"/>
-      <c r="H292" s="63" t="inlineStr"/>
-      <c r="I292" s="63" t="inlineStr"/>
-      <c r="J292" s="23" t="inlineStr"/>
+      <c r="G292" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H292" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I292" s="63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J292" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K292" s="23" t="n"/>
       <c r="L292" s="64" t="inlineStr"/>
     </row>
